--- a/src/attributions/attributions_ig_traj_387.xlsx
+++ b/src/attributions/attributions_ig_traj_387.xlsx
@@ -2140,103 +2140,103 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>0.08214573442150336</v>
+        <v>0.1256799013590874</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.01913091250795114</v>
+        <v>-0.02006297572136219</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.06783295964632886</v>
+        <v>-0.09919005244172559</v>
       </c>
       <c r="G4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K4" t="n">
-        <v>0.04374061722760308</v>
+        <v>0.1555087908618455</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.01601042827184657</v>
+        <v>-0.02348829060682501</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.06806945814449135</v>
+        <v>-0.07343387910886254</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.00127763642506507</v>
+        <v>0.005595338785644562</v>
       </c>
       <c r="U4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.005179785805066455</v>
+        <v>0.03019153730758447</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.003906712873628661</v>
+        <v>0.01366128509743723</v>
       </c>
       <c r="Y4" t="n">
         <v>-0</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB4" t="n">
         <v>-0</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.01353631510922677</v>
+        <v>-0.05804418950990773</v>
       </c>
       <c r="AD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.03280408339186123</v>
+        <v>-0.08651162226232192</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.001905284614872888</v>
+        <v>-0.06804059826892432</v>
       </c>
       <c r="AH4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
         <v>-0</v>
@@ -2248,7 +2248,7 @@
         <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.01463004144606882</v>
+        <v>0.01299954430666915</v>
       </c>
       <c r="AM4" t="n">
         <v>0</v>
@@ -2257,13 +2257,13 @@
         <v>0</v>
       </c>
       <c r="AO4" t="n">
-        <v>-0.01537401704868254</v>
+        <v>-0.04176200390798705</v>
       </c>
       <c r="AP4" t="n">
-        <v>-0.02159545745949689</v>
+        <v>-0.03855307891261981</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
@@ -2272,10 +2272,10 @@
         <v>0</v>
       </c>
       <c r="AT4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.09105212106193691</v>
+        <v>0.3412624180278637</v>
       </c>
       <c r="AV4" t="n">
         <v>-0</v>
@@ -2284,79 +2284,79 @@
         <v>0</v>
       </c>
       <c r="AX4" t="n">
-        <v>-0.01526628099689282</v>
+        <v>-0.05965039189019351</v>
       </c>
       <c r="AY4" t="n">
-        <v>-0.07592718349233926</v>
+        <v>-0.04632234947365369</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA4" t="n">
         <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC4" t="n">
         <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.01609377305862226</v>
+        <v>-0.006548684329683768</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF4" t="n">
         <v>0</v>
       </c>
       <c r="BG4" t="n">
-        <v>-0.01768080216797477</v>
+        <v>-0.03244953997207146</v>
       </c>
       <c r="BH4" t="n">
-        <v>-0.007841393694710463</v>
+        <v>-0.01702251201956372</v>
       </c>
       <c r="BI4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.0319128188397069</v>
+        <v>0.051220647254791</v>
       </c>
       <c r="BN4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO4" t="n">
         <v>-0</v>
       </c>
       <c r="BP4" t="n">
-        <v>-0.003647862114621259</v>
+        <v>0.08079818629998277</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.01649874335623537</v>
+        <v>0.07469493147134419</v>
       </c>
       <c r="BR4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU4" t="n">
         <v>-0</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.04650874583189769</v>
+        <v>0.1337071291289867</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
@@ -2365,25 +2365,25 @@
         <v>0</v>
       </c>
       <c r="BY4" t="n">
-        <v>-0.01859549098041675</v>
+        <v>-0.07650299065601308</v>
       </c>
       <c r="BZ4" t="n">
-        <v>-0.01321289771740155</v>
+        <v>-0.1044912808105972</v>
       </c>
       <c r="CA4" t="n">
         <v>-0</v>
       </c>
       <c r="CB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD4" t="n">
         <v>-0</v>
       </c>
       <c r="CE4" t="n">
-        <v>-0.02107107276171988</v>
+        <v>-0.0480306197054676</v>
       </c>
       <c r="CF4" t="n">
         <v>0</v>
@@ -2392,121 +2392,121 @@
         <v>-0</v>
       </c>
       <c r="CH4" t="n">
-        <v>-0.002646902308021943</v>
+        <v>0.00149013065972294</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.03874116252610966</v>
+        <v>0.07138807527127139</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK4" t="n">
         <v>0</v>
       </c>
       <c r="CL4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.004748909550564845</v>
+        <v>-0.1323458667504452</v>
       </c>
       <c r="CO4" t="n">
         <v>-0</v>
       </c>
       <c r="CP4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.004927767134596817</v>
+        <v>0.09067677045687947</v>
       </c>
       <c r="CR4" t="n">
-        <v>-0.00858316222266505</v>
+        <v>0.05590443616912703</v>
       </c>
       <c r="CS4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW4" t="n">
-        <v>-0.01638430205458732</v>
+        <v>-0.05275485491502645</v>
       </c>
       <c r="CX4" t="n">
         <v>-0</v>
       </c>
       <c r="CY4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ4" t="n">
-        <v>-0.00633651791362662</v>
+        <v>-0.01135934600682707</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.04061827773051321</v>
+        <v>0.06443497745073419</v>
       </c>
       <c r="DB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE4" t="n">
         <v>0</v>
       </c>
       <c r="DF4" t="n">
-        <v>-0.01395165406102096</v>
+        <v>-0.001410875149716108</v>
       </c>
       <c r="DG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.01693230385582111</v>
+        <v>-0.06602526871443358</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.05862285434455801</v>
+        <v>-0.001390977486573557</v>
       </c>
       <c r="DK4" t="n">
         <v>0</v>
       </c>
       <c r="DL4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN4" t="n">
         <v>-0</v>
       </c>
       <c r="DO4" t="n">
-        <v>-0.01215479320441775</v>
+        <v>-0.03536800163195334</v>
       </c>
       <c r="DP4" t="n">
         <v>0</v>
       </c>
       <c r="DQ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.02093979523954334</v>
+        <v>0.05197372720903288</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.01397479280713661</v>
+        <v>0.09775590575440551</v>
       </c>
       <c r="DT4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
@@ -2518,19 +2518,19 @@
         <v>-0</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.005529809601643417</v>
+        <v>-0.009569829167283918</v>
       </c>
       <c r="DY4" t="n">
         <v>0</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA4" t="n">
-        <v>-0.00104190625958732</v>
+        <v>0.003742123383516765</v>
       </c>
       <c r="EB4" t="n">
-        <v>-0.0337432897036585</v>
+        <v>-0.06917413167570514</v>
       </c>
       <c r="EC4" t="n">
         <v>-0</v>
@@ -2542,64 +2542,64 @@
         <v>0</v>
       </c>
       <c r="EF4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG4" t="n">
-        <v>-0.00707322460622516</v>
+        <v>-0.0454875420406398</v>
       </c>
       <c r="EH4" t="n">
         <v>-0</v>
       </c>
       <c r="EI4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ4" t="n">
-        <v>-0.005007470524747527</v>
+        <v>-0.04826354513371694</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.01436041773935234</v>
+        <v>0.0373199349643482</v>
       </c>
       <c r="EL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP4" t="n">
-        <v>-0.0044724658078243</v>
+        <v>0.02766533339060391</v>
       </c>
       <c r="EQ4" t="n">
         <v>-0</v>
       </c>
       <c r="ER4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES4" t="n">
-        <v>-0.01662081524248301</v>
+        <v>-0.05744966678361397</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.04209120874618848</v>
+        <v>0.05022864774409799</v>
       </c>
       <c r="EU4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW4" t="n">
         <v>0</v>
       </c>
       <c r="EX4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY4" t="n">
-        <v>-0.01709802969959982</v>
+        <v>-0.05917602933527941</v>
       </c>
       <c r="EZ4" t="n">
         <v>-0</v>
@@ -2608,37 +2608,37 @@
         <v>0</v>
       </c>
       <c r="FB4" t="n">
-        <v>-0.004038213153856682</v>
+        <v>-0.01896120037776205</v>
       </c>
       <c r="FC4" t="n">
-        <v>0.03739611603264326</v>
+        <v>0.05561840145292068</v>
       </c>
       <c r="FD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE4" t="n">
         <v>0</v>
       </c>
       <c r="FF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG4" t="n">
         <v>0</v>
       </c>
       <c r="FH4" t="n">
-        <v>-0.01721168603669605</v>
+        <v>-0.09870915959123437</v>
       </c>
       <c r="FI4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ4" t="n">
         <v>-0</v>
       </c>
       <c r="FK4" t="n">
-        <v>-0.01266862786867706</v>
+        <v>0.02552345048252706</v>
       </c>
       <c r="FL4" t="n">
-        <v>0.006771015974397479</v>
+        <v>-0.03874369346610721</v>
       </c>
       <c r="FM4" t="n">
         <v>0</v>
@@ -2647,25 +2647,25 @@
         <v>-0</v>
       </c>
       <c r="FO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP4" t="n">
         <v>-0</v>
       </c>
       <c r="FQ4" t="n">
-        <v>0.0004028115297530461</v>
+        <v>0.04766876217438597</v>
       </c>
       <c r="FR4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS4" t="n">
         <v>-0</v>
       </c>
       <c r="FT4" t="n">
-        <v>-0.005659639322422538</v>
+        <v>0.007870922269589692</v>
       </c>
       <c r="FU4" t="n">
-        <v>0.03697223092929056</v>
+        <v>0.04912458680460185</v>
       </c>
       <c r="FV4" t="n">
         <v>-0</v>
@@ -2674,13 +2674,13 @@
         <v>-0</v>
       </c>
       <c r="FX4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ4" t="n">
-        <v>-0.0203997494781948</v>
+        <v>-0.003088088893511781</v>
       </c>
       <c r="GA4" t="n">
         <v>0</v>
@@ -2689,19 +2689,19 @@
         <v>-0</v>
       </c>
       <c r="GC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD4" t="n">
-        <v>-0.01158145825348885</v>
+        <v>0.04572447689016281</v>
       </c>
       <c r="GE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GF4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="5">
@@ -2709,43 +2709,43 @@
         <v>-0</v>
       </c>
       <c r="B5" t="n">
-        <v>0.1850262090325384</v>
+        <v>0.2230455339916937</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0739457252075945</v>
+        <v>-0.09876188482643897</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.08822875280844984</v>
+        <v>-0.03532647177358764</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H5" t="n">
         <v>-0</v>
       </c>
       <c r="I5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>-0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1013544575443146</v>
+        <v>0.1791574999903162</v>
       </c>
       <c r="L5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.02482183930750002</v>
+        <v>-0.050709893234283</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.07880665851633568</v>
+        <v>-0.05580230662946421</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -2760,22 +2760,22 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.837445897461488e-11</v>
+        <v>3.260331707736187e-11</v>
       </c>
       <c r="U5" t="n">
         <v>-0</v>
       </c>
       <c r="V5" t="n">
-        <v>-4.009741021240289e-12</v>
+        <v>-6.793130890462245e-12</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.003297921500067322</v>
+        <v>0.0001846918346955422</v>
       </c>
       <c r="X5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
         <v>-0</v>
@@ -2784,49 +2784,49 @@
         <v>-0</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.07455936139169973</v>
+        <v>-0.02502899385664853</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.008748743496095949</v>
+        <v>-0.07586512747827495</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.02539742544180152</v>
+        <v>-0.08032467302233058</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH5" t="n">
         <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL5" t="n">
-        <v>-0.01589909874085663</v>
+        <v>0.1076735659463635</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0.04546821402884443</v>
+        <v>-0.02972599023596645</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.09962175883419581</v>
+        <v>0.04615147996307423</v>
       </c>
       <c r="AP5" t="n">
         <v>0</v>
@@ -2835,31 +2835,31 @@
         <v>-0</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT5" t="n">
         <v>-0</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.3525297250416867</v>
+        <v>0.3102331151439105</v>
       </c>
       <c r="AV5" t="n">
         <v>-0</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.0008355857290802148</v>
+        <v>-0.1325029745268939</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.132544859219493</v>
+        <v>-0.148303603632734</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA5" t="n">
         <v>0</v>
@@ -2868,19 +2868,19 @@
         <v>-0</v>
       </c>
       <c r="BC5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>-0.002131580382741768</v>
+        <v>-0.01499131314729523</v>
       </c>
       <c r="BE5" t="n">
         <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>-0.03533213145886058</v>
+        <v>-0.005193943090366314</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.05964730472572649</v>
+        <v>-0.0124087663738808</v>
       </c>
       <c r="BH5" t="n">
         <v>0</v>
@@ -2889,31 +2889,31 @@
         <v>-0</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK5" t="n">
         <v>0</v>
       </c>
       <c r="BL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.1235026456314869</v>
+        <v>-0.002308789508002276</v>
       </c>
       <c r="BN5" t="n">
         <v>-0</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.0409302940226959</v>
+        <v>0.04675365391908019</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.1432491999916329</v>
+        <v>0.08025008285144321</v>
       </c>
       <c r="BQ5" t="n">
         <v>-0</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS5" t="n">
         <v>-0</v>
@@ -2925,52 +2925,52 @@
         <v>-0</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.1788181425964334</v>
+        <v>0.2123171562424091</v>
       </c>
       <c r="BW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX5" t="n">
-        <v>2.418860652726503e-05</v>
+        <v>-0.1124485275552855</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.02862957594109864</v>
+        <v>-0.02140836628751771</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.05244900957007197</v>
+        <v>-0.1121066101665672</v>
       </c>
       <c r="CF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.0173389535984131</v>
+        <v>0.0869923552342235</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.002548643250462707</v>
+        <v>0.02465823920595515</v>
       </c>
       <c r="CI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ5" t="n">
         <v>-0</v>
       </c>
       <c r="CK5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL5" t="n">
         <v>-0</v>
@@ -2979,22 +2979,22 @@
         <v>0</v>
       </c>
       <c r="CN5" t="n">
-        <v>-0.03160850073189755</v>
+        <v>-0.09395668711804842</v>
       </c>
       <c r="CO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP5" t="n">
-        <v>-0.05634780643783325</v>
+        <v>0.0777172674587648</v>
       </c>
       <c r="CQ5" t="n">
-        <v>-0.1451649897265145</v>
+        <v>0.06909712200816819</v>
       </c>
       <c r="CR5" t="n">
         <v>0</v>
       </c>
       <c r="CS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT5" t="n">
         <v>-0</v>
@@ -3003,22 +3003,22 @@
         <v>-0</v>
       </c>
       <c r="CV5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW5" t="n">
-        <v>-0.03149250069204444</v>
+        <v>-0.1169483248488462</v>
       </c>
       <c r="CX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.03575504965287382</v>
+        <v>0.1010040656768496</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.02147526787022046</v>
+        <v>0.02691420958241151</v>
       </c>
       <c r="DA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB5" t="n">
         <v>0</v>
@@ -3033,22 +3033,22 @@
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>-0.001404015594251884</v>
+        <v>-0.005257679672054743</v>
       </c>
       <c r="DG5" t="n">
         <v>0</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.02240512975192933</v>
+        <v>0.02661896862023285</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.009340065067753396</v>
+        <v>-0.08531108019899106</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL5" t="n">
         <v>0</v>
@@ -3060,52 +3060,52 @@
         <v>-0</v>
       </c>
       <c r="DO5" t="n">
-        <v>-0.06422048560447932</v>
+        <v>-0.06819176646131654</v>
       </c>
       <c r="DP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ5" t="n">
-        <v>-0.02138961312813754</v>
+        <v>0.04044732564956627</v>
       </c>
       <c r="DR5" t="n">
-        <v>-0.01980500850164947</v>
+        <v>-0.02577193010448142</v>
       </c>
       <c r="DS5" t="n">
         <v>-0</v>
       </c>
       <c r="DT5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX5" t="n">
-        <v>0.02742099939766514</v>
+        <v>0.06397760484248891</v>
       </c>
       <c r="DY5" t="n">
         <v>0</v>
       </c>
       <c r="DZ5" t="n">
-        <v>-0.04995822605533638</v>
+        <v>0.02417955414189256</v>
       </c>
       <c r="EA5" t="n">
-        <v>-0.03229662945717256</v>
+        <v>-0.04223551831428903</v>
       </c>
       <c r="EB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC5" t="n">
         <v>-0</v>
       </c>
       <c r="ED5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE5" t="n">
         <v>-0</v>
@@ -3114,19 +3114,19 @@
         <v>0</v>
       </c>
       <c r="EG5" t="n">
-        <v>-0.03230381516321944</v>
+        <v>-0.06830058698265601</v>
       </c>
       <c r="EH5" t="n">
         <v>-0</v>
       </c>
       <c r="EI5" t="n">
-        <v>0.05194440642616283</v>
+        <v>0.1054365141099054</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.0871428889675059</v>
+        <v>0.03076242285014836</v>
       </c>
       <c r="EK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL5" t="n">
         <v>-0</v>
@@ -3141,70 +3141,70 @@
         <v>0</v>
       </c>
       <c r="EP5" t="n">
-        <v>-0.03762404423239918</v>
+        <v>-0.05927942835753744</v>
       </c>
       <c r="EQ5" t="n">
         <v>-0</v>
       </c>
       <c r="ER5" t="n">
-        <v>0.04064883848566187</v>
+        <v>0.05829628002353888</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.01022884356063061</v>
+        <v>-0.03411981198597615</v>
       </c>
       <c r="ET5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV5" t="n">
         <v>-0</v>
       </c>
       <c r="EW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY5" t="n">
-        <v>-0.03968085439558475</v>
+        <v>-0.1240512470485583</v>
       </c>
       <c r="EZ5" t="n">
         <v>-0</v>
       </c>
       <c r="FA5" t="n">
-        <v>0.0342020742566838</v>
+        <v>0.1018604494627476</v>
       </c>
       <c r="FB5" t="n">
-        <v>0.02256030572288495</v>
+        <v>0.01446391054764952</v>
       </c>
       <c r="FC5" t="n">
         <v>-0</v>
       </c>
       <c r="FD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF5" t="n">
         <v>-0</v>
       </c>
       <c r="FG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH5" t="n">
-        <v>0.0569468861728995</v>
+        <v>-0.04389401231817888</v>
       </c>
       <c r="FI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ5" t="n">
-        <v>-0.06208659662424184</v>
+        <v>-0.04272143066841897</v>
       </c>
       <c r="FK5" t="n">
-        <v>-0.01583742689418433</v>
+        <v>0.02597695770906724</v>
       </c>
       <c r="FL5" t="n">
         <v>-0</v>
@@ -3213,28 +3213,28 @@
         <v>0</v>
       </c>
       <c r="FN5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ5" t="n">
-        <v>-0.04728543683042601</v>
+        <v>0.0145832551651505</v>
       </c>
       <c r="FR5" t="n">
         <v>-0</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.03623196866609824</v>
+        <v>0.1150268543390245</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.06072624471701864</v>
+        <v>-0.0547651600096555</v>
       </c>
       <c r="FU5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV5" t="n">
         <v>-0</v>
@@ -3246,22 +3246,22 @@
         <v>0</v>
       </c>
       <c r="FY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ5" t="n">
-        <v>-0.03463743330072951</v>
+        <v>-0.09888104505806596</v>
       </c>
       <c r="GA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB5" t="n">
-        <v>-0.009438428490801603</v>
+        <v>0.05848115903969042</v>
       </c>
       <c r="GC5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE5" t="n">
         <v>-0</v>
@@ -3275,22 +3275,22 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B6" t="n">
-        <v>0.02758468984329142</v>
+        <v>0.03535576281510418</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.01797212562789362</v>
+        <v>0.0206757506448489</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.009602825404416798</v>
+        <v>-0.01617826806329399</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -3302,25 +3302,25 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.007493283853484898</v>
+        <v>0.05154872734052166</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0222413103694277</v>
+        <v>0.01211013803939575</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.01166633611938843</v>
+        <v>-0.0141691205507403</v>
       </c>
       <c r="P6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -3329,10 +3329,10 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.000459385868965544</v>
+        <v>-0.0001522847476956348</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -3341,43 +3341,43 @@
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>-4.122289957046226e-13</v>
+        <v>-1.32571586395233e-11</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.004900766268989622</v>
+        <v>4.342560289650521e-05</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z6" t="n">
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB6" t="n">
         <v>-0</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.02179328308179952</v>
+        <v>-0.01506256470164139</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.02925356702532132</v>
+        <v>-0.05784790863295888</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.003828641123606861</v>
+        <v>-0.01567063944865544</v>
       </c>
       <c r="AH6" t="n">
         <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ6" t="n">
         <v>-0</v>
@@ -3386,7 +3386,7 @@
         <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.004003869457291205</v>
+        <v>0.01102686267739746</v>
       </c>
       <c r="AM6" t="n">
         <v>0</v>
@@ -3395,52 +3395,52 @@
         <v>0</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.02245485441372601</v>
+        <v>-0.01367293884846872</v>
       </c>
       <c r="AP6" t="n">
-        <v>-0.005680384663042289</v>
+        <v>-0.02403655185199708</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS6" t="n">
         <v>0</v>
       </c>
       <c r="AT6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.05520854726722267</v>
+        <v>0.09388067648524789</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW6" t="n">
         <v>0</v>
       </c>
       <c r="AX6" t="n">
-        <v>-0.01153047276568847</v>
+        <v>-0.01736530800042364</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0.01190400454645855</v>
+        <v>-0.0176513964458848</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA6" t="n">
         <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.00393964046015192</v>
+        <v>-0.004642782943788158</v>
       </c>
       <c r="BE6" t="n">
         <v>0</v>
@@ -3449,13 +3449,13 @@
         <v>0</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.01522614369221218</v>
+        <v>-0.007150644690059726</v>
       </c>
       <c r="BH6" t="n">
-        <v>0.001548376432925018</v>
+        <v>0.002220621992809765</v>
       </c>
       <c r="BI6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ6" t="n">
         <v>0</v>
@@ -3464,37 +3464,37 @@
         <v>0</v>
       </c>
       <c r="BL6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.0357843735629183</v>
+        <v>0.01789149164238709</v>
       </c>
       <c r="BN6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO6" t="n">
         <v>-0</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.01497594228538059</v>
+        <v>0.04016969167449728</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.01288337878144544</v>
+        <v>0.03248913739779999</v>
       </c>
       <c r="BR6" t="n">
         <v>-0</v>
       </c>
       <c r="BS6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT6" t="n">
         <v>0</v>
       </c>
       <c r="BU6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.01681556064756924</v>
+        <v>0.03950555910044894</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
@@ -3503,13 +3503,13 @@
         <v>0</v>
       </c>
       <c r="BY6" t="n">
-        <v>-0.01387590216502263</v>
+        <v>0.001798352067260921</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0.0178806770371268</v>
+        <v>-0.03540455851126135</v>
       </c>
       <c r="CA6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB6" t="n">
         <v>0</v>
@@ -3521,76 +3521,76 @@
         <v>-0</v>
       </c>
       <c r="CE6" t="n">
-        <v>-0.001442888832453634</v>
+        <v>-0.0099450027584373</v>
       </c>
       <c r="CF6" t="n">
         <v>0</v>
       </c>
       <c r="CG6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH6" t="n">
-        <v>-0.0002974510133814744</v>
+        <v>-0.002291553392325787</v>
       </c>
       <c r="CI6" t="n">
-        <v>0.006666525213917775</v>
+        <v>0.02302553445158865</v>
       </c>
       <c r="CJ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL6" t="n">
         <v>-0</v>
       </c>
       <c r="CM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN6" t="n">
-        <v>-0.0005720696776688587</v>
+        <v>-0.03337189992354664</v>
       </c>
       <c r="CO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.001016362012112679</v>
+        <v>0.04176702500136321</v>
       </c>
       <c r="CR6" t="n">
-        <v>-0.01207545635112781</v>
+        <v>0.02607349495747704</v>
       </c>
       <c r="CS6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT6" t="n">
         <v>-0</v>
       </c>
       <c r="CU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV6" t="n">
         <v>0</v>
       </c>
       <c r="CW6" t="n">
-        <v>0.00380697083895547</v>
+        <v>-0.01270270245836435</v>
       </c>
       <c r="CX6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CY6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ6" t="n">
-        <v>0.001014792649864582</v>
+        <v>-0.004181970573929268</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.005595884972824366</v>
+        <v>0.02028902142553031</v>
       </c>
       <c r="DB6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC6" t="n">
         <v>0</v>
@@ -3599,22 +3599,22 @@
         <v>0</v>
       </c>
       <c r="DE6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF6" t="n">
-        <v>-0.001123729468771648</v>
+        <v>-0.0161848272078865</v>
       </c>
       <c r="DG6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI6" t="n">
-        <v>-0.00031189740420467</v>
+        <v>-0.001020499976067624</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0.0231761463406691</v>
+        <v>-0.002576574548495515</v>
       </c>
       <c r="DK6" t="n">
         <v>0</v>
@@ -3623,28 +3623,28 @@
         <v>-0</v>
       </c>
       <c r="DM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN6" t="n">
         <v>-0</v>
       </c>
       <c r="DO6" t="n">
-        <v>0.002336493413922938</v>
+        <v>-0.01467577413612469</v>
       </c>
       <c r="DP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR6" t="n">
-        <v>0.0166795349989682</v>
+        <v>-0.0004251948740876655</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.002888798620690069</v>
+        <v>0.0304078861889196</v>
       </c>
       <c r="DT6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU6" t="n">
         <v>-0</v>
@@ -3653,10 +3653,10 @@
         <v>-0</v>
       </c>
       <c r="DW6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX6" t="n">
-        <v>-0.01208803338650998</v>
+        <v>-0.01227002319666336</v>
       </c>
       <c r="DY6" t="n">
         <v>0</v>
@@ -3665,94 +3665,94 @@
         <v>-0</v>
       </c>
       <c r="EA6" t="n">
-        <v>-0.008952547927859121</v>
+        <v>0.003018876912366041</v>
       </c>
       <c r="EB6" t="n">
-        <v>-0.001984830274798916</v>
+        <v>0.02294095397547401</v>
       </c>
       <c r="EC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE6" t="n">
         <v>-0</v>
       </c>
       <c r="EF6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG6" t="n">
-        <v>0.006965980992411702</v>
+        <v>-0.01022195580715228</v>
       </c>
       <c r="EH6" t="n">
         <v>-0</v>
       </c>
       <c r="EI6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.001414257203462974</v>
+        <v>-0.02117936941579021</v>
       </c>
       <c r="EK6" t="n">
-        <v>0.001867243265850634</v>
+        <v>0.003153739331548244</v>
       </c>
       <c r="EL6" t="n">
         <v>-0</v>
       </c>
       <c r="EM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN6" t="n">
         <v>-0</v>
       </c>
       <c r="EO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP6" t="n">
-        <v>-0.0002797262369646898</v>
+        <v>0.0007329350274278261</v>
       </c>
       <c r="EQ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES6" t="n">
-        <v>-0.01765893499562844</v>
+        <v>-0.001412223695881717</v>
       </c>
       <c r="ET6" t="n">
-        <v>0.03378819555814749</v>
+        <v>0.01425306028006251</v>
       </c>
       <c r="EU6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV6" t="n">
         <v>0</v>
       </c>
       <c r="EW6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX6" t="n">
         <v>-0</v>
       </c>
       <c r="EY6" t="n">
-        <v>0.00426378942653754</v>
+        <v>-0.01626978050951014</v>
       </c>
       <c r="EZ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FA6" t="n">
         <v>0</v>
       </c>
       <c r="FB6" t="n">
-        <v>0.000487067115732075</v>
+        <v>-0.009464183854876235</v>
       </c>
       <c r="FC6" t="n">
-        <v>0.009789737144459316</v>
+        <v>0.0148699056698475</v>
       </c>
       <c r="FD6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE6" t="n">
         <v>-0</v>
@@ -3761,22 +3761,22 @@
         <v>-0</v>
       </c>
       <c r="FG6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH6" t="n">
-        <v>-0.007850121079093261</v>
+        <v>-0.01859695070510998</v>
       </c>
       <c r="FI6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ6" t="n">
         <v>-0</v>
       </c>
       <c r="FK6" t="n">
-        <v>-0.01513942483999426</v>
+        <v>0.01547068860696225</v>
       </c>
       <c r="FL6" t="n">
-        <v>0.02050011411704178</v>
+        <v>0.004450892189997865</v>
       </c>
       <c r="FM6" t="n">
         <v>0</v>
@@ -3785,13 +3785,13 @@
         <v>-0</v>
       </c>
       <c r="FO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ6" t="n">
-        <v>-0.01054628926062933</v>
+        <v>0.01331409187522092</v>
       </c>
       <c r="FR6" t="n">
         <v>-0</v>
@@ -3800,10 +3800,10 @@
         <v>-0</v>
       </c>
       <c r="FT6" t="n">
-        <v>-0.003315740762804567</v>
+        <v>0.000804620389033593</v>
       </c>
       <c r="FU6" t="n">
-        <v>0.004933424648197187</v>
+        <v>-0.03398972399904942</v>
       </c>
       <c r="FV6" t="n">
         <v>-0</v>
@@ -3812,13 +3812,13 @@
         <v>-0</v>
       </c>
       <c r="FX6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ6" t="n">
-        <v>-0.02366752214168198</v>
+        <v>0.01037233718294694</v>
       </c>
       <c r="GA6" t="n">
         <v>0</v>
@@ -3830,7 +3830,7 @@
         <v>-0</v>
       </c>
       <c r="GD6" t="n">
-        <v>-0.005232287434426565</v>
+        <v>0.01639184438198207</v>
       </c>
       <c r="GE6" t="n">
         <v>0</v>
@@ -3847,7 +3847,7 @@
         <v>0</v>
       </c>
       <c r="B7" t="n">
-        <v>0.1136616185004456</v>
+        <v>0.0573518042972172</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -3856,25 +3856,25 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.01854177320546914</v>
+        <v>-0.02676838159101288</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H7" t="n">
         <v>-0</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.02133704245934901</v>
+        <v>-0.007057602313463602</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.04809840817911103</v>
+        <v>0.07402638238624655</v>
       </c>
       <c r="L7" t="n">
         <v>-0</v>
@@ -3883,7 +3883,7 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.06512794450610694</v>
+        <v>-0.02665358968567567</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -3892,16 +3892,16 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.02353313422806881</v>
+        <v>-0.005369242946556717</v>
       </c>
       <c r="S7" t="n">
         <v>-0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.003758571446441068</v>
+        <v>-0.001507091930849239</v>
       </c>
       <c r="U7" t="n">
         <v>-0</v>
@@ -3910,34 +3910,34 @@
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.00129149916023891</v>
+        <v>-0.002719283594926718</v>
       </c>
       <c r="X7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.0004448356820049264</v>
+        <v>0.000961460737100391</v>
       </c>
       <c r="AB7" t="n">
         <v>-0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.04070378227423674</v>
+        <v>-0.01361907425259898</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.02587750341297962</v>
+        <v>-0.01898289872968168</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
@@ -3946,16 +3946,16 @@
         <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.01493582182036787</v>
+        <v>-0.0001051820220446573</v>
       </c>
       <c r="AK7" t="n">
         <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.03142282596730562</v>
+        <v>0.02483853653902312</v>
       </c>
       <c r="AM7" t="n">
         <v>0</v>
@@ -3964,37 +3964,37 @@
         <v>0</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.02729864662053499</v>
+        <v>-0.006590284219735204</v>
       </c>
       <c r="AP7" t="n">
         <v>0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS7" t="n">
-        <v>-0.01743481365086592</v>
+        <v>-0.005011213703880194</v>
       </c>
       <c r="AT7" t="n">
         <v>-0</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.192722986532962</v>
+        <v>0.094778811000074</v>
       </c>
       <c r="AV7" t="n">
         <v>-0</v>
       </c>
       <c r="AW7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.07329278521945905</v>
+        <v>-0.0174764137535097</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ7" t="n">
         <v>0</v>
@@ -4003,94 +4003,94 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>-0.0001107656759079732</v>
+        <v>0.009383007091098731</v>
       </c>
       <c r="BC7" t="n">
         <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>-0.01206911466189209</v>
+        <v>-0.003082402385925087</v>
       </c>
       <c r="BE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BF7" t="n">
         <v>0</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.04141537813921098</v>
+        <v>-0.01367802355946967</v>
       </c>
       <c r="BH7" t="n">
         <v>0</v>
       </c>
       <c r="BI7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.00934073746760569</v>
+        <v>0.005072329183352309</v>
       </c>
       <c r="BL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.02159103998878574</v>
+        <v>0.01331214487509609</v>
       </c>
       <c r="BN7" t="n">
         <v>-0</v>
       </c>
       <c r="BO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.08355596209678617</v>
+        <v>0.03739835410054387</v>
       </c>
       <c r="BQ7" t="n">
         <v>-0</v>
       </c>
       <c r="BR7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS7" t="n">
         <v>-0</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.02811358808801904</v>
+        <v>0.01195143015429514</v>
       </c>
       <c r="BU7" t="n">
         <v>-0</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.09907319534906581</v>
+        <v>0.05064529586867214</v>
       </c>
       <c r="BW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.01000535705964963</v>
+        <v>-0.02111705631060218</v>
       </c>
       <c r="BZ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB7" t="n">
         <v>0</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.009473760225144612</v>
+        <v>-0.01736598863998806</v>
       </c>
       <c r="CD7" t="n">
         <v>-0</v>
       </c>
       <c r="CE7" t="n">
-        <v>-0.0231151977950157</v>
+        <v>-0.02277185157774838</v>
       </c>
       <c r="CF7" t="n">
         <v>-0</v>
@@ -4099,10 +4099,10 @@
         <v>-0</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.0007992666277344224</v>
+        <v>0.008686911326119548</v>
       </c>
       <c r="CI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ7" t="n">
         <v>-0</v>
@@ -4111,25 +4111,25 @@
         <v>0</v>
       </c>
       <c r="CL7" t="n">
-        <v>0.02914680365957997</v>
+        <v>0.01158285425053303</v>
       </c>
       <c r="CM7" t="n">
         <v>0</v>
       </c>
       <c r="CN7" t="n">
-        <v>-0.02372517519996744</v>
+        <v>-0.04272934241421225</v>
       </c>
       <c r="CO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP7" t="n">
         <v>-0</v>
       </c>
       <c r="CQ7" t="n">
-        <v>-0.01955311313188933</v>
+        <v>0.006636114760391161</v>
       </c>
       <c r="CR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS7" t="n">
         <v>-0</v>
@@ -4138,13 +4138,13 @@
         <v>-0</v>
       </c>
       <c r="CU7" t="n">
-        <v>-0.01041606192927356</v>
+        <v>0.01725272219563892</v>
       </c>
       <c r="CV7" t="n">
         <v>0</v>
       </c>
       <c r="CW7" t="n">
-        <v>-0.01852686148374278</v>
+        <v>-0.02357828221133119</v>
       </c>
       <c r="CX7" t="n">
         <v>0</v>
@@ -4153,34 +4153,34 @@
         <v>0</v>
       </c>
       <c r="CZ7" t="n">
-        <v>0.006287272948533196</v>
+        <v>0.004800055541532795</v>
       </c>
       <c r="DA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB7" t="n">
         <v>0</v>
       </c>
       <c r="DC7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD7" t="n">
-        <v>0.02895363816332878</v>
+        <v>0.01076333087451401</v>
       </c>
       <c r="DE7" t="n">
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>-0.07700324203984658</v>
+        <v>-0.01765400908101899</v>
       </c>
       <c r="DG7" t="n">
         <v>-0</v>
       </c>
       <c r="DH7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.02928948984498936</v>
+        <v>-0.01109622247621334</v>
       </c>
       <c r="DJ7" t="n">
         <v>-0</v>
@@ -4189,97 +4189,97 @@
         <v>0</v>
       </c>
       <c r="DL7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM7" t="n">
-        <v>-0.007881298973856277</v>
+        <v>-0.005858993441534721</v>
       </c>
       <c r="DN7" t="n">
         <v>-0</v>
       </c>
       <c r="DO7" t="n">
-        <v>0.0006514658011524504</v>
+        <v>-0.01825107309409244</v>
       </c>
       <c r="DP7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR7" t="n">
-        <v>-0.00495292225081246</v>
+        <v>0.008833481520610385</v>
       </c>
       <c r="DS7" t="n">
         <v>-0</v>
       </c>
       <c r="DT7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU7" t="n">
         <v>-0</v>
       </c>
       <c r="DV7" t="n">
-        <v>7.29775030925512e-05</v>
+        <v>-0.02676431056182765</v>
       </c>
       <c r="DW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX7" t="n">
-        <v>-0.00284268102385678</v>
+        <v>0.008786451508595064</v>
       </c>
       <c r="DY7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ7" t="n">
         <v>-0</v>
       </c>
       <c r="EA7" t="n">
-        <v>-0.01782610710586427</v>
+        <v>0.006918968254542759</v>
       </c>
       <c r="EB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC7" t="n">
         <v>-0</v>
       </c>
       <c r="ED7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE7" t="n">
-        <v>-0.009557320894835604</v>
+        <v>-0.007585490843401093</v>
       </c>
       <c r="EF7" t="n">
         <v>0</v>
       </c>
       <c r="EG7" t="n">
-        <v>-0.002001867775117797</v>
+        <v>-0.01847197174787972</v>
       </c>
       <c r="EH7" t="n">
         <v>0</v>
       </c>
       <c r="EI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.03054384964539728</v>
+        <v>0.0005447764992909224</v>
       </c>
       <c r="EK7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM7" t="n">
         <v>0</v>
       </c>
       <c r="EN7" t="n">
-        <v>0.03116203686820392</v>
+        <v>0.004467748781259449</v>
       </c>
       <c r="EO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP7" t="n">
-        <v>-0.03731047938797516</v>
+        <v>-0.00376861019713078</v>
       </c>
       <c r="EQ7" t="n">
         <v>-0</v>
@@ -4288,25 +4288,25 @@
         <v>-0</v>
       </c>
       <c r="ES7" t="n">
-        <v>-0.005324279878063002</v>
+        <v>0.00514855990223742</v>
       </c>
       <c r="ET7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV7" t="n">
         <v>0</v>
       </c>
       <c r="EW7" t="n">
-        <v>0.0129949029744163</v>
+        <v>0.006846586439442157</v>
       </c>
       <c r="EX7" t="n">
         <v>-0</v>
       </c>
       <c r="EY7" t="n">
-        <v>-0.02989463240446355</v>
+        <v>-0.02723991604087954</v>
       </c>
       <c r="EZ7" t="n">
         <v>-0</v>
@@ -4315,7 +4315,7 @@
         <v>-0</v>
       </c>
       <c r="FB7" t="n">
-        <v>0.007010908084441859</v>
+        <v>0.001875281755083035</v>
       </c>
       <c r="FC7" t="n">
         <v>-0</v>
@@ -4327,40 +4327,40 @@
         <v>0</v>
       </c>
       <c r="FF7" t="n">
-        <v>0.01679123726348924</v>
+        <v>0.01148960407910633</v>
       </c>
       <c r="FG7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH7" t="n">
-        <v>-0.03180431943795009</v>
+        <v>-0.01672225865036832</v>
       </c>
       <c r="FI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK7" t="n">
-        <v>-0.02314821104298326</v>
+        <v>0.007835942321912275</v>
       </c>
       <c r="FL7" t="n">
         <v>0</v>
       </c>
       <c r="FM7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO7" t="n">
-        <v>0.01321263881745623</v>
+        <v>0.03862971493796271</v>
       </c>
       <c r="FP7" t="n">
         <v>-0</v>
       </c>
       <c r="FQ7" t="n">
-        <v>-0.05221328933133468</v>
+        <v>0.007430799794086331</v>
       </c>
       <c r="FR7" t="n">
         <v>-0</v>
@@ -4369,7 +4369,7 @@
         <v>-0</v>
       </c>
       <c r="FT7" t="n">
-        <v>0.01307906002836827</v>
+        <v>-0.018479604423926</v>
       </c>
       <c r="FU7" t="n">
         <v>0</v>
@@ -4378,19 +4378,19 @@
         <v>-0</v>
       </c>
       <c r="FW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX7" t="n">
-        <v>0.0004167813294005878</v>
+        <v>0.001925968409180166</v>
       </c>
       <c r="FY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ7" t="n">
-        <v>-0.03966815641694523</v>
+        <v>-0.01217532935620078</v>
       </c>
       <c r="GA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB7" t="n">
         <v>-0</v>
@@ -4399,16 +4399,16 @@
         <v>0</v>
       </c>
       <c r="GD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE7" t="n">
         <v>-0</v>
       </c>
       <c r="GF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG7" t="n">
-        <v>0.03590524781603489</v>
+        <v>0.001663933263182766</v>
       </c>
     </row>
     <row r="8">
@@ -4982,25 +4982,25 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3103561414237541</v>
+        <v>0.2008855970274953</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1531024932183861</v>
+        <v>-0.09153885801406174</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.03633587329307112</v>
+        <v>-0.06156411863383257</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H9" t="n">
         <v>-0</v>
@@ -5012,97 +5012,97 @@
         <v>-0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1719411355610549</v>
+        <v>0.1808355272181053</v>
       </c>
       <c r="L9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.1434774565282382</v>
+        <v>-0.1303153649960409</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.09746305553680817</v>
+        <v>-0.1243343226838883</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.03521904209986356</v>
+        <v>0.02784425995934603</v>
       </c>
       <c r="U9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>0.003484730919290808</v>
+        <v>-0.004341789896906976</v>
       </c>
       <c r="W9" t="n">
-        <v>0.002019854932342002</v>
+        <v>-0.01281953675044371</v>
       </c>
       <c r="X9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
         <v>-0</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
         <v>-0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.1433504238963448</v>
+        <v>-0.01406735161283178</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0.05851450483662803</v>
+        <v>-0.07250923502755831</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.03854312138031091</v>
+        <v>-0.1288328446882808</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH9" t="n">
         <v>-0</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL9" t="n">
-        <v>-0.005168095342208977</v>
+        <v>0.1665809030637409</v>
       </c>
       <c r="AM9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>-0.03490268283106915</v>
+        <v>-0.06952529942357523</v>
       </c>
       <c r="AO9" t="n">
-        <v>-0.1223394724633551</v>
+        <v>0.06176595392615105</v>
       </c>
       <c r="AP9" t="n">
         <v>0</v>
@@ -5111,28 +5111,28 @@
         <v>0</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT9" t="n">
         <v>-0</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.4735324936435902</v>
+        <v>0.2429543553072513</v>
       </c>
       <c r="AV9" t="n">
         <v>-0</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.0357432730598158</v>
+        <v>-0.0258186409530377</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.2144125234783662</v>
+        <v>-0.3003137522824589</v>
       </c>
       <c r="AY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ9" t="n">
         <v>0</v>
@@ -5147,16 +5147,16 @@
         <v>-0</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.002183454793054325</v>
+        <v>-0.03087800596318795</v>
       </c>
       <c r="BE9" t="n">
         <v>0</v>
       </c>
       <c r="BF9" t="n">
-        <v>-0.0561963265519158</v>
+        <v>-0.007068604938110655</v>
       </c>
       <c r="BG9" t="n">
-        <v>-0.1273189780987195</v>
+        <v>0.004693375277908484</v>
       </c>
       <c r="BH9" t="n">
         <v>0</v>
@@ -5165,7 +5165,7 @@
         <v>-0</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK9" t="n">
         <v>0</v>
@@ -5174,19 +5174,19 @@
         <v>-0</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.2042493519358677</v>
+        <v>0.0137764250376857</v>
       </c>
       <c r="BN9" t="n">
         <v>-0</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.01334239410733215</v>
+        <v>0.0162388785271594</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.1677908150616915</v>
+        <v>0.013879185128857</v>
       </c>
       <c r="BQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR9" t="n">
         <v>-0</v>
@@ -5201,52 +5201,52 @@
         <v>-0</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.25090901623241</v>
+        <v>0.2249934654153383</v>
       </c>
       <c r="BW9" t="n">
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.02149425048705285</v>
+        <v>-0.1674830898494268</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.04884207975885654</v>
+        <v>-0.07550797954764492</v>
       </c>
       <c r="BZ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB9" t="n">
         <v>0</v>
       </c>
       <c r="CC9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD9" t="n">
         <v>-0</v>
       </c>
       <c r="CE9" t="n">
-        <v>-0.06748941604910144</v>
+        <v>-0.0736525623030956</v>
       </c>
       <c r="CF9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.004410314597794694</v>
+        <v>0.08566135246651686</v>
       </c>
       <c r="CH9" t="n">
-        <v>-0.01547372102438291</v>
+        <v>0.03122145579907007</v>
       </c>
       <c r="CI9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL9" t="n">
         <v>-0</v>
@@ -5255,25 +5255,25 @@
         <v>0</v>
       </c>
       <c r="CN9" t="n">
-        <v>-0.1087723285376849</v>
+        <v>-0.08835971330864897</v>
       </c>
       <c r="CO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP9" t="n">
-        <v>-0.1524190033034282</v>
+        <v>0.2439601621369039</v>
       </c>
       <c r="CQ9" t="n">
-        <v>-0.1083886026351612</v>
+        <v>0.1363598807853237</v>
       </c>
       <c r="CR9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS9" t="n">
         <v>-0</v>
       </c>
       <c r="CT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU9" t="n">
         <v>-0</v>
@@ -5282,25 +5282,25 @@
         <v>0</v>
       </c>
       <c r="CW9" t="n">
-        <v>-0.03734569545117718</v>
+        <v>-0.05588706321200394</v>
       </c>
       <c r="CX9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.029858200771021</v>
+        <v>0.09773153156386311</v>
       </c>
       <c r="CZ9" t="n">
-        <v>-0.001233737288401999</v>
+        <v>0.04857790714559689</v>
       </c>
       <c r="DA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD9" t="n">
         <v>0</v>
@@ -5309,22 +5309,22 @@
         <v>-0</v>
       </c>
       <c r="DF9" t="n">
-        <v>-0.01739343052257666</v>
+        <v>-0.006631269195297653</v>
       </c>
       <c r="DG9" t="n">
         <v>0</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.01789753748655446</v>
+        <v>0.01533180604995437</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.03754547421124504</v>
+        <v>-0.03504989983289861</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL9" t="n">
         <v>0</v>
@@ -5336,52 +5336,52 @@
         <v>-0</v>
       </c>
       <c r="DO9" t="n">
-        <v>-0.06870910375041643</v>
+        <v>-0.07992726256119825</v>
       </c>
       <c r="DP9" t="n">
         <v>0</v>
       </c>
       <c r="DQ9" t="n">
-        <v>-0.05741984156332924</v>
+        <v>0.06686863603844727</v>
       </c>
       <c r="DR9" t="n">
-        <v>-0.0005178719901881206</v>
+        <v>0.02607982720398423</v>
       </c>
       <c r="DS9" t="n">
         <v>0</v>
       </c>
       <c r="DT9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX9" t="n">
-        <v>0.03057806092138517</v>
+        <v>0.01868312899901028</v>
       </c>
       <c r="DY9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ9" t="n">
-        <v>-0.04289285222413675</v>
+        <v>0.03875777121204517</v>
       </c>
       <c r="EA9" t="n">
-        <v>-0.03066918440722576</v>
+        <v>-0.03808056910043373</v>
       </c>
       <c r="EB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC9" t="n">
         <v>0</v>
       </c>
       <c r="ED9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE9" t="n">
         <v>-0</v>
@@ -5390,22 +5390,22 @@
         <v>-0</v>
       </c>
       <c r="EG9" t="n">
-        <v>-0.0009089258758161764</v>
+        <v>0.009860078233819382</v>
       </c>
       <c r="EH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI9" t="n">
-        <v>0.06466902582078619</v>
+        <v>0.05543964929756663</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.05549012941577131</v>
+        <v>0.03753053827510593</v>
       </c>
       <c r="EK9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM9" t="n">
         <v>-0</v>
@@ -5414,25 +5414,25 @@
         <v>-0</v>
       </c>
       <c r="EO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP9" t="n">
-        <v>-0.07686679980056092</v>
+        <v>-0.07609819328059872</v>
       </c>
       <c r="EQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER9" t="n">
-        <v>-0.06464132722335067</v>
+        <v>-0.08545439555327801</v>
       </c>
       <c r="ES9" t="n">
-        <v>-0.01387655890485309</v>
+        <v>0.00538340056937289</v>
       </c>
       <c r="ET9" t="n">
         <v>-0</v>
       </c>
       <c r="EU9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV9" t="n">
         <v>0</v>
@@ -5444,106 +5444,106 @@
         <v>-0</v>
       </c>
       <c r="EY9" t="n">
-        <v>-0.05014886794441304</v>
+        <v>-0.07313264307180636</v>
       </c>
       <c r="EZ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FA9" t="n">
-        <v>0.01611673868950689</v>
+        <v>0.1101930724433627</v>
       </c>
       <c r="FB9" t="n">
-        <v>0.01904479004526298</v>
+        <v>0.0291777716608328</v>
       </c>
       <c r="FC9" t="n">
         <v>-0</v>
       </c>
       <c r="FD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF9" t="n">
         <v>-0</v>
       </c>
       <c r="FG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH9" t="n">
-        <v>0.06227071933161356</v>
+        <v>-0.01996500218591554</v>
       </c>
       <c r="FI9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ9" t="n">
-        <v>0.04275476510703501</v>
+        <v>0.01500561471217129</v>
       </c>
       <c r="FK9" t="n">
-        <v>-0.003649854358932698</v>
+        <v>-0.03343905116603629</v>
       </c>
       <c r="FL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ9" t="n">
-        <v>-0.06807668951862966</v>
+        <v>0.0227162013678158</v>
       </c>
       <c r="FR9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS9" t="n">
-        <v>-0.06063628624048316</v>
+        <v>0.1010383283090918</v>
       </c>
       <c r="FT9" t="n">
-        <v>0.1018028673906357</v>
+        <v>-0.1184175212228915</v>
       </c>
       <c r="FU9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX9" t="n">
         <v>0</v>
       </c>
       <c r="FY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ9" t="n">
-        <v>-0.03938758513184229</v>
+        <v>-0.005478934658069293</v>
       </c>
       <c r="GA9" t="n">
         <v>-0</v>
       </c>
       <c r="GB9" t="n">
-        <v>-0.07484534556923945</v>
+        <v>0.03448430678171262</v>
       </c>
       <c r="GC9" t="n">
         <v>0</v>
       </c>
       <c r="GD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE9" t="n">
         <v>-0</v>
       </c>
       <c r="GF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG9" t="n">
         <v>0</v>
@@ -5554,16 +5554,16 @@
         <v>0</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4259816322032363</v>
+        <v>0.2252560503610018</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.1678744880613211</v>
+        <v>-0.2490338628059737</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1581149287746292</v>
+        <v>-0.08188993695590252</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -5572,7 +5572,7 @@
         <v>-0</v>
       </c>
       <c r="H10" t="n">
-        <v>0.006561357342530764</v>
+        <v>0.02443911113667726</v>
       </c>
       <c r="I10" t="n">
         <v>-0</v>
@@ -5581,16 +5581,16 @@
         <v>-0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2424388421192752</v>
+        <v>0.194605297174175</v>
       </c>
       <c r="L10" t="n">
         <v>-0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.1454847835175078</v>
+        <v>-0.2780867494165519</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2424578537558282</v>
+        <v>-0.1490742882696002</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -5599,115 +5599,115 @@
         <v>-0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.0009850086416229938</v>
+        <v>-2.02139029899196e-05</v>
       </c>
       <c r="R10" t="n">
         <v>-0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.09088965558007735</v>
+        <v>0.06405323810127181</v>
       </c>
       <c r="U10" t="n">
         <v>-0</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.01976525665681013</v>
+        <v>-0.0334010372387754</v>
       </c>
       <c r="W10" t="n">
-        <v>0.003405376770020749</v>
+        <v>-0.07141183785875273</v>
       </c>
       <c r="X10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>-0.0003933462052886738</v>
+        <v>-0.001048846128231731</v>
       </c>
       <c r="AA10" t="n">
         <v>-0</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.09771221088317091</v>
+        <v>-0.1364521107413056</v>
       </c>
       <c r="AD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.08638746714185556</v>
+        <v>-0.04977601191469872</v>
       </c>
       <c r="AF10" t="n">
-        <v>-0.04634338211217969</v>
+        <v>-0.1165364891380153</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH10" t="n">
         <v>-0</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.01334733170365163</v>
+        <v>0.04138630752832338</v>
       </c>
       <c r="AJ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.01744155403331334</v>
+        <v>0.1237119425231522</v>
       </c>
       <c r="AM10" t="n">
         <v>-0</v>
       </c>
       <c r="AN10" t="n">
-        <v>-0.07169906677231733</v>
+        <v>-0.04826966797352459</v>
       </c>
       <c r="AO10" t="n">
-        <v>-0.104048537040536</v>
+        <v>0.05933051914992168</v>
       </c>
       <c r="AP10" t="n">
         <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.01763712554206695</v>
+        <v>0.01423274992103907</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT10" t="n">
         <v>-0</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.6366770696999785</v>
+        <v>0.2636517317822323</v>
       </c>
       <c r="AV10" t="n">
         <v>-0</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.01032794043049731</v>
+        <v>-0.08421503497671734</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.215736254214151</v>
+        <v>-0.3727853143100651</v>
       </c>
       <c r="AY10" t="n">
         <v>-0</v>
       </c>
       <c r="AZ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.06969946094683648</v>
+        <v>-0.07862414752669201</v>
       </c>
       <c r="BB10" t="n">
         <v>-0</v>
@@ -5716,16 +5716,16 @@
         <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.006406151268222776</v>
+        <v>-0.0406215543446839</v>
       </c>
       <c r="BE10" t="n">
         <v>0</v>
       </c>
       <c r="BF10" t="n">
-        <v>-0.06222297306098423</v>
+        <v>-0.08396421884951191</v>
       </c>
       <c r="BG10" t="n">
-        <v>-0.2690975732869395</v>
+        <v>-0.02579472047656723</v>
       </c>
       <c r="BH10" t="n">
         <v>0</v>
@@ -5734,34 +5734,34 @@
         <v>-0</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.001923159870027743</v>
+        <v>-0.03391608254562539</v>
       </c>
       <c r="BK10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL10" t="n">
         <v>-0</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.2569773498871126</v>
+        <v>0.04048515157005733</v>
       </c>
       <c r="BN10" t="n">
         <v>-0</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.1370813408178907</v>
+        <v>0.1265319860104111</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.1846019276839643</v>
+        <v>-0.0310551878292342</v>
       </c>
       <c r="BQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS10" t="n">
-        <v>0.04697994608930468</v>
+        <v>0.03969481209360948</v>
       </c>
       <c r="BT10" t="n">
         <v>-0</v>
@@ -5770,25 +5770,25 @@
         <v>-0</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.3127585727104896</v>
+        <v>0.2459144132434282</v>
       </c>
       <c r="BW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX10" t="n">
-        <v>0.04482540117108109</v>
+        <v>-0.2146318811465657</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.05496414106500923</v>
+        <v>-0.200335111458538</v>
       </c>
       <c r="BZ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.008647107870544025</v>
+        <v>-0.1080742274998577</v>
       </c>
       <c r="CC10" t="n">
         <v>-0</v>
@@ -5797,16 +5797,16 @@
         <v>-0</v>
       </c>
       <c r="CE10" t="n">
-        <v>-0.09902904275398759</v>
+        <v>-0.05979544021395375</v>
       </c>
       <c r="CF10" t="n">
         <v>-0</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.01996449091116983</v>
+        <v>0.1604301217245037</v>
       </c>
       <c r="CH10" t="n">
-        <v>-0.0004176427909376596</v>
+        <v>0.04247590053664639</v>
       </c>
       <c r="CI10" t="n">
         <v>-0</v>
@@ -5815,7 +5815,7 @@
         <v>-0</v>
       </c>
       <c r="CK10" t="n">
-        <v>0.004828318560303349</v>
+        <v>-0.03048913647494816</v>
       </c>
       <c r="CL10" t="n">
         <v>-0</v>
@@ -5824,43 +5824,43 @@
         <v>0</v>
       </c>
       <c r="CN10" t="n">
-        <v>-0.1473390314580556</v>
+        <v>-0.01260422809517705</v>
       </c>
       <c r="CO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP10" t="n">
-        <v>-0.1645562788891195</v>
+        <v>0.2347797922133201</v>
       </c>
       <c r="CQ10" t="n">
-        <v>-0.05776533041925666</v>
+        <v>0.341500655075098</v>
       </c>
       <c r="CR10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS10" t="n">
         <v>-0</v>
       </c>
       <c r="CT10" t="n">
-        <v>0.06153593110143597</v>
+        <v>0.05594574107434089</v>
       </c>
       <c r="CU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW10" t="n">
-        <v>-0.06377439262864654</v>
+        <v>-0.05310197748433505</v>
       </c>
       <c r="CX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.052887794659549</v>
+        <v>0.1823879146373675</v>
       </c>
       <c r="CZ10" t="n">
-        <v>0.004266494971241605</v>
+        <v>0.05616952849891358</v>
       </c>
       <c r="DA10" t="n">
         <v>0</v>
@@ -5869,25 +5869,25 @@
         <v>0</v>
       </c>
       <c r="DC10" t="n">
-        <v>0.004846749556149256</v>
+        <v>-0.01494986455130795</v>
       </c>
       <c r="DD10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF10" t="n">
-        <v>-0.07149671914322794</v>
+        <v>-0.05413594235424746</v>
       </c>
       <c r="DG10" t="n">
         <v>0</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.03324769077944559</v>
+        <v>0.07035620009667667</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.003653520914688366</v>
+        <v>-0.001876519789238907</v>
       </c>
       <c r="DJ10" t="n">
         <v>0</v>
@@ -5896,25 +5896,25 @@
         <v>-0</v>
       </c>
       <c r="DL10" t="n">
-        <v>-0.0005866103922514802</v>
+        <v>-0.0569123668784703</v>
       </c>
       <c r="DM10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO10" t="n">
-        <v>-0.1077615797002603</v>
+        <v>-0.03029882470245524</v>
       </c>
       <c r="DP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ10" t="n">
-        <v>-0.04455372880747833</v>
+        <v>0.1424453804828975</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.03466910121297651</v>
+        <v>-0.06184094872602346</v>
       </c>
       <c r="DS10" t="n">
         <v>-0</v>
@@ -5923,25 +5923,25 @@
         <v>-0</v>
       </c>
       <c r="DU10" t="n">
-        <v>-0.02380560453415971</v>
+        <v>0.09974479068449654</v>
       </c>
       <c r="DV10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX10" t="n">
-        <v>-0.02385684209118821</v>
+        <v>0.05983930729938169</v>
       </c>
       <c r="DY10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ10" t="n">
-        <v>-0.05006853825129523</v>
+        <v>0.03284535878631944</v>
       </c>
       <c r="EA10" t="n">
-        <v>-0.07101320543931398</v>
+        <v>-0.1185973397174184</v>
       </c>
       <c r="EB10" t="n">
         <v>0</v>
@@ -5950,25 +5950,25 @@
         <v>-0</v>
       </c>
       <c r="ED10" t="n">
-        <v>-0.02349156797692327</v>
+        <v>0.1464963626674377</v>
       </c>
       <c r="EE10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG10" t="n">
-        <v>-0.04675462537943386</v>
+        <v>0.03270898537930295</v>
       </c>
       <c r="EH10" t="n">
         <v>-0</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.07376137341166529</v>
+        <v>0.09742589178109655</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.04513579232119509</v>
+        <v>0.05302247475468726</v>
       </c>
       <c r="EK10" t="n">
         <v>-0</v>
@@ -5977,106 +5977,106 @@
         <v>-0</v>
       </c>
       <c r="EM10" t="n">
-        <v>0.03979686016907934</v>
+        <v>-0.0384627888578581</v>
       </c>
       <c r="EN10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO10" t="n">
         <v>0</v>
       </c>
       <c r="EP10" t="n">
-        <v>-0.1066917646332838</v>
+        <v>-0.0354055497789312</v>
       </c>
       <c r="EQ10" t="n">
         <v>-0</v>
       </c>
       <c r="ER10" t="n">
-        <v>0.09323422890608676</v>
+        <v>0.1676561169701913</v>
       </c>
       <c r="ES10" t="n">
-        <v>-0.03430629954353511</v>
+        <v>-0.07630186288093065</v>
       </c>
       <c r="ET10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV10" t="n">
-        <v>-0.002292134528121338</v>
+        <v>0.02143684868243962</v>
       </c>
       <c r="EW10" t="n">
         <v>-0</v>
       </c>
       <c r="EX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY10" t="n">
-        <v>-0.07341195343361456</v>
+        <v>-0.07017227778591284</v>
       </c>
       <c r="EZ10" t="n">
         <v>-0</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.03905863709187449</v>
+        <v>0.2143476145987197</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.0286662288610752</v>
+        <v>0.05552280179138252</v>
       </c>
       <c r="FC10" t="n">
         <v>-0</v>
       </c>
       <c r="FD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE10" t="n">
-        <v>0.003168026049479378</v>
+        <v>-0.01659140011918108</v>
       </c>
       <c r="FF10" t="n">
         <v>-0</v>
       </c>
       <c r="FG10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.07416874783723988</v>
+        <v>-0.03028214911052357</v>
       </c>
       <c r="FI10" t="n">
         <v>0</v>
       </c>
       <c r="FJ10" t="n">
-        <v>-0.05626234468681927</v>
+        <v>-0.08798156344082338</v>
       </c>
       <c r="FK10" t="n">
-        <v>-0.03406945509610364</v>
+        <v>0.07493550204033717</v>
       </c>
       <c r="FL10" t="n">
         <v>-0</v>
       </c>
       <c r="FM10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN10" t="n">
-        <v>0.007778484432980369</v>
+        <v>-0.0345238796699721</v>
       </c>
       <c r="FO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ10" t="n">
-        <v>-0.1180833787114379</v>
+        <v>0.05563028836035827</v>
       </c>
       <c r="FR10" t="n">
         <v>0</v>
       </c>
       <c r="FS10" t="n">
-        <v>-0.08371431783589488</v>
+        <v>0.1036375672960823</v>
       </c>
       <c r="FT10" t="n">
-        <v>-0.0756125073020821</v>
+        <v>-0.2138985626407092</v>
       </c>
       <c r="FU10" t="n">
         <v>0</v>
@@ -6085,34 +6085,34 @@
         <v>-0</v>
       </c>
       <c r="FW10" t="n">
-        <v>0.01218161400947745</v>
+        <v>-0.08051937746300249</v>
       </c>
       <c r="FX10" t="n">
         <v>0</v>
       </c>
       <c r="FY10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ10" t="n">
-        <v>-0.1173292123265021</v>
+        <v>-0.01959376083339393</v>
       </c>
       <c r="GA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB10" t="n">
-        <v>-0.03425425906610514</v>
+        <v>0.07705358429423489</v>
       </c>
       <c r="GC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE10" t="n">
         <v>-0</v>
       </c>
       <c r="GF10" t="n">
-        <v>0.03444463729654101</v>
+        <v>-0.05902252232636873</v>
       </c>
       <c r="GG10" t="n">
         <v>-0</v>
@@ -6120,28 +6120,28 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B11" t="n">
-        <v>0.2003284532055637</v>
+        <v>0.350829191223558</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.1475623248632727</v>
+        <v>-0.04532044638291593</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.08074645436325685</v>
+        <v>-0.1899703278977005</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -6150,7 +6150,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1185087633909166</v>
+        <v>0.4299122235631717</v>
       </c>
       <c r="L11" t="n">
         <v>-0</v>
@@ -6159,13 +6159,13 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.1413290486698002</v>
+        <v>-0.1238413795950612</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.08430843292753641</v>
+        <v>-0.147595959631512</v>
       </c>
       <c r="P11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -6177,46 +6177,46 @@
         <v>-0</v>
       </c>
       <c r="T11" t="n">
-        <v>0.03148873614599242</v>
+        <v>0.06449908146754801</v>
       </c>
       <c r="U11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0.00745900907387284</v>
+        <v>-0.06423898311895826</v>
       </c>
       <c r="X11" t="n">
-        <v>0.027630779722285</v>
+        <v>0.01484412015088111</v>
       </c>
       <c r="Y11" t="n">
         <v>-0</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB11" t="n">
         <v>-0</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.04760265263627353</v>
+        <v>-0.01933619030408277</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.02549786818196067</v>
+        <v>-0.2467265504766255</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.02186477612432299</v>
+        <v>0.02809594793048386</v>
       </c>
       <c r="AH11" t="n">
         <v>-0</v>
@@ -6231,22 +6231,22 @@
         <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.04250454511073189</v>
+        <v>0.08894237159947803</v>
       </c>
       <c r="AM11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN11" t="n">
         <v>0</v>
       </c>
       <c r="AO11" t="n">
-        <v>-0.03100252085691105</v>
+        <v>-0.07502909360024805</v>
       </c>
       <c r="AP11" t="n">
-        <v>-0.01902414223660397</v>
+        <v>-0.03775031629538851</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR11" t="n">
         <v>-0</v>
@@ -6255,91 +6255,91 @@
         <v>0</v>
       </c>
       <c r="AT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.2296194076938837</v>
+        <v>0.5618144423062735</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW11" t="n">
         <v>0</v>
       </c>
       <c r="AX11" t="n">
-        <v>-0.03495690208675777</v>
+        <v>-0.2673726273305581</v>
       </c>
       <c r="AY11" t="n">
-        <v>-0.01518128096352984</v>
+        <v>-0.04925258806201532</v>
       </c>
       <c r="AZ11" t="n">
         <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC11" t="n">
         <v>0</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.04018408696850691</v>
+        <v>-0.05484582454472139</v>
       </c>
       <c r="BE11" t="n">
         <v>0</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BG11" t="n">
-        <v>-0.09738925687967685</v>
+        <v>-0.03328507796691149</v>
       </c>
       <c r="BH11" t="n">
-        <v>-0.05267289082667884</v>
+        <v>-0.08469730820175093</v>
       </c>
       <c r="BI11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK11" t="n">
         <v>0</v>
       </c>
       <c r="BL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.1157616528818147</v>
+        <v>0.1491462336141437</v>
       </c>
       <c r="BN11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO11" t="n">
         <v>-0</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.07499205992429689</v>
+        <v>0.1458371818542306</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0.03730946728959354</v>
+        <v>0.08882946399936689</v>
       </c>
       <c r="BR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU11" t="n">
         <v>-0</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.1114951927906827</v>
+        <v>0.3614054809549952</v>
       </c>
       <c r="BW11" t="n">
         <v>0</v>
@@ -6348,67 +6348,67 @@
         <v>0</v>
       </c>
       <c r="BY11" t="n">
-        <v>-0.0217464235473953</v>
+        <v>-0.1067589774672117</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0.02788688088198231</v>
+        <v>-0.03685028959844906</v>
       </c>
       <c r="CA11" t="n">
         <v>-0</v>
       </c>
       <c r="CB11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE11" t="n">
-        <v>-0.03787204636942135</v>
+        <v>-0.1241092025518976</v>
       </c>
       <c r="CF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG11" t="n">
         <v>-0</v>
       </c>
       <c r="CH11" t="n">
-        <v>0.01828749644702544</v>
+        <v>0.01978470935278656</v>
       </c>
       <c r="CI11" t="n">
-        <v>0.02221124817930002</v>
+        <v>0.07338608075269119</v>
       </c>
       <c r="CJ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM11" t="n">
         <v>0</v>
       </c>
       <c r="CN11" t="n">
-        <v>-0.0478193260196479</v>
+        <v>-0.251802387437423</v>
       </c>
       <c r="CO11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP11" t="n">
         <v>-0</v>
       </c>
       <c r="CQ11" t="n">
-        <v>-0.04661937826973361</v>
+        <v>0.1221697069623804</v>
       </c>
       <c r="CR11" t="n">
-        <v>-0.01678308079201058</v>
+        <v>0.01343929829129181</v>
       </c>
       <c r="CS11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT11" t="n">
         <v>-0</v>
@@ -6417,28 +6417,28 @@
         <v>0</v>
       </c>
       <c r="CV11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW11" t="n">
-        <v>-0.01887795156493464</v>
+        <v>-0.1064851511679312</v>
       </c>
       <c r="CX11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY11" t="n">
         <v>0</v>
       </c>
       <c r="CZ11" t="n">
-        <v>0.01670171850675937</v>
+        <v>-0.004151412469944357</v>
       </c>
       <c r="DA11" t="n">
-        <v>0.02665433713015996</v>
+        <v>0.07506648731206986</v>
       </c>
       <c r="DB11" t="n">
         <v>0</v>
       </c>
       <c r="DC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD11" t="n">
         <v>0</v>
@@ -6447,7 +6447,7 @@
         <v>-0</v>
       </c>
       <c r="DF11" t="n">
-        <v>-0.0543402585817394</v>
+        <v>-0.09080405628058692</v>
       </c>
       <c r="DG11" t="n">
         <v>-0</v>
@@ -6456,37 +6456,37 @@
         <v>-0</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.01866677175554392</v>
+        <v>-0.1459155087432904</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0.001260152459815914</v>
+        <v>-0.01112350658612769</v>
       </c>
       <c r="DK11" t="n">
         <v>0</v>
       </c>
       <c r="DL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN11" t="n">
         <v>-0</v>
       </c>
       <c r="DO11" t="n">
-        <v>-0.04340219876955471</v>
+        <v>-0.07141902223784129</v>
       </c>
       <c r="DP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR11" t="n">
-        <v>0.01947734612864144</v>
+        <v>-0.02432997313869871</v>
       </c>
       <c r="DS11" t="n">
-        <v>-0.04351804856657359</v>
+        <v>-0.02078030157929265</v>
       </c>
       <c r="DT11" t="n">
         <v>-0</v>
@@ -6498,10 +6498,10 @@
         <v>-0</v>
       </c>
       <c r="DW11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX11" t="n">
-        <v>-0.004184235193898932</v>
+        <v>0.08051332131484186</v>
       </c>
       <c r="DY11" t="n">
         <v>0</v>
@@ -6510,124 +6510,124 @@
         <v>-0</v>
       </c>
       <c r="EA11" t="n">
-        <v>-0.04656214785294661</v>
+        <v>-0.01104297412681744</v>
       </c>
       <c r="EB11" t="n">
-        <v>-0.03125452410825783</v>
+        <v>0.04511286355344563</v>
       </c>
       <c r="EC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE11" t="n">
         <v>-0</v>
       </c>
       <c r="EF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG11" t="n">
-        <v>0.004853959791523563</v>
+        <v>0.01303916692887764</v>
       </c>
       <c r="EH11" t="n">
         <v>-0</v>
       </c>
       <c r="EI11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.01685700137050789</v>
+        <v>-0.0555714445095503</v>
       </c>
       <c r="EK11" t="n">
-        <v>0.006152105506792397</v>
+        <v>0.07331798587748441</v>
       </c>
       <c r="EL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN11" t="n">
         <v>-0</v>
       </c>
       <c r="EO11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP11" t="n">
-        <v>0.01969455823828409</v>
+        <v>0.01067497146155001</v>
       </c>
       <c r="EQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES11" t="n">
-        <v>-0.002970332440473214</v>
+        <v>-0.1359050193981318</v>
       </c>
       <c r="ET11" t="n">
-        <v>0.0416060696336296</v>
+        <v>0.04873687353802514</v>
       </c>
       <c r="EU11" t="n">
         <v>-0</v>
       </c>
       <c r="EV11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW11" t="n">
         <v>0</v>
       </c>
       <c r="EX11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY11" t="n">
-        <v>-0.01538083057491701</v>
+        <v>-0.1375259138729545</v>
       </c>
       <c r="EZ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA11" t="n">
         <v>-0</v>
       </c>
       <c r="FB11" t="n">
-        <v>0.01457960315726394</v>
+        <v>-0.01554307142266503</v>
       </c>
       <c r="FC11" t="n">
-        <v>0.0335829905423381</v>
+        <v>0.05454722534975368</v>
       </c>
       <c r="FD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH11" t="n">
-        <v>-0.03350183050263326</v>
+        <v>-0.1340294653705559</v>
       </c>
       <c r="FI11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ11" t="n">
         <v>-0</v>
       </c>
       <c r="FK11" t="n">
-        <v>-0.04281291736431082</v>
+        <v>0.1571221262706473</v>
       </c>
       <c r="FL11" t="n">
-        <v>0.02362509599704034</v>
+        <v>0.02811191808488273</v>
       </c>
       <c r="FM11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO11" t="n">
         <v>0</v>
@@ -6636,34 +6636,34 @@
         <v>0</v>
       </c>
       <c r="FQ11" t="n">
-        <v>0.0008852507065909865</v>
+        <v>0.07725201497597896</v>
       </c>
       <c r="FR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS11" t="n">
         <v>-0</v>
       </c>
       <c r="FT11" t="n">
-        <v>-0.01970076736575571</v>
+        <v>-0.1216046978509652</v>
       </c>
       <c r="FU11" t="n">
-        <v>0.008508216419464813</v>
+        <v>-0.007516212023089866</v>
       </c>
       <c r="FV11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ11" t="n">
-        <v>-0.05907635415833178</v>
+        <v>-0.07075737311067094</v>
       </c>
       <c r="GA11" t="n">
         <v>0</v>
@@ -6675,7 +6675,7 @@
         <v>-0</v>
       </c>
       <c r="GD11" t="n">
-        <v>-0.02950596986048984</v>
+        <v>0.07834869629055122</v>
       </c>
       <c r="GE11" t="n">
         <v>-0</v>
@@ -6692,22 +6692,22 @@
         <v>0</v>
       </c>
       <c r="B12" t="n">
-        <v>0.2783507899448683</v>
+        <v>0.2365751584439963</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.1567698305669457</v>
+        <v>-0.1053233090207516</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.04314019691998732</v>
+        <v>-0.08234204879513253</v>
       </c>
       <c r="F12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H12" t="n">
         <v>-0</v>
@@ -6716,49 +6716,49 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1695493465461461</v>
+        <v>0.2393306220775195</v>
       </c>
       <c r="L12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.1460438177712817</v>
+        <v>-0.1373662129269638</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.07068547598809212</v>
+        <v>-0.1327432994073908</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T12" t="n">
-        <v>0.06816521374358819</v>
+        <v>0.04566461522373319</v>
       </c>
       <c r="U12" t="n">
         <v>-0</v>
       </c>
       <c r="V12" t="n">
-        <v>0.009884813846848074</v>
+        <v>-0.01083987606529292</v>
       </c>
       <c r="W12" t="n">
-        <v>0.03626935587268824</v>
+        <v>-0.0286641535990955</v>
       </c>
       <c r="X12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
         <v>-0</v>
@@ -6770,82 +6770,82 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.1223743137842651</v>
+        <v>-0.01832907606988095</v>
       </c>
       <c r="AD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>-0.009103857370985907</v>
+        <v>-0.1189026057410813</v>
       </c>
       <c r="AF12" t="n">
-        <v>-0.01232410258183162</v>
+        <v>-0.09622734301835106</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>-0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.007647578302124945</v>
+        <v>0.1348477133135225</v>
       </c>
       <c r="AM12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>-0.02732571383253406</v>
+        <v>-0.0744123058707078</v>
       </c>
       <c r="AO12" t="n">
-        <v>-0.0749886288473362</v>
+        <v>0.06422545300288465</v>
       </c>
       <c r="AP12" t="n">
         <v>0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.3634289500555293</v>
+        <v>0.2307971402950729</v>
       </c>
       <c r="AV12" t="n">
         <v>-0</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.0408371135029624</v>
+        <v>-0.01843280939890201</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.1137185054932755</v>
+        <v>-0.1869625380148911</v>
       </c>
       <c r="AY12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ12" t="n">
         <v>0</v>
       </c>
       <c r="BA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB12" t="n">
         <v>-0</v>
@@ -6854,25 +6854,25 @@
         <v>-0</v>
       </c>
       <c r="BD12" t="n">
-        <v>-0.005875582175542297</v>
+        <v>-0.02586004405665123</v>
       </c>
       <c r="BE12" t="n">
         <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>-0.08049838926111079</v>
+        <v>-0.03701343010687867</v>
       </c>
       <c r="BG12" t="n">
-        <v>-0.1311431836514666</v>
+        <v>-0.01008088006774013</v>
       </c>
       <c r="BH12" t="n">
         <v>0</v>
       </c>
       <c r="BI12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK12" t="n">
         <v>0</v>
@@ -6881,22 +6881,22 @@
         <v>-0</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.1258414886290692</v>
+        <v>0.04304386765471432</v>
       </c>
       <c r="BN12" t="n">
         <v>-0</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.006283049525998104</v>
+        <v>0.009054712719969526</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.1193214249294913</v>
+        <v>0.1039637367225385</v>
       </c>
       <c r="BQ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS12" t="n">
         <v>-0</v>
@@ -6908,25 +6908,25 @@
         <v>-0</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.1928304181295795</v>
+        <v>0.2183963731470048</v>
       </c>
       <c r="BW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX12" t="n">
-        <v>0.02653467436267144</v>
+        <v>-0.06681950443234326</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.0735219653762739</v>
+        <v>-0.06106939676632986</v>
       </c>
       <c r="BZ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC12" t="n">
         <v>0</v>
@@ -6935,19 +6935,19 @@
         <v>-0</v>
       </c>
       <c r="CE12" t="n">
-        <v>-0.05938162090734363</v>
+        <v>-0.08717526733885771</v>
       </c>
       <c r="CF12" t="n">
         <v>-0</v>
       </c>
       <c r="CG12" t="n">
-        <v>0.0002289857809065573</v>
+        <v>0.07784868708150673</v>
       </c>
       <c r="CH12" t="n">
-        <v>-0.01107734973589113</v>
+        <v>0.04576609575229743</v>
       </c>
       <c r="CI12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ12" t="n">
         <v>-0</v>
@@ -6962,19 +6962,19 @@
         <v>0</v>
       </c>
       <c r="CN12" t="n">
-        <v>-0.07336132852384401</v>
+        <v>-0.1442043317591996</v>
       </c>
       <c r="CO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP12" t="n">
-        <v>-0.1253255707566642</v>
+        <v>0.2305108710008206</v>
       </c>
       <c r="CQ12" t="n">
-        <v>-0.05700117785781658</v>
+        <v>0.0775741137024073</v>
       </c>
       <c r="CR12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS12" t="n">
         <v>-0</v>
@@ -6989,16 +6989,16 @@
         <v>0</v>
       </c>
       <c r="CW12" t="n">
-        <v>-0.02715547390201285</v>
+        <v>-0.06478296799400729</v>
       </c>
       <c r="CX12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY12" t="n">
-        <v>0.01742061893772363</v>
+        <v>0.08640847447472466</v>
       </c>
       <c r="CZ12" t="n">
-        <v>-0.007051517132674867</v>
+        <v>0.05127616163306513</v>
       </c>
       <c r="DA12" t="n">
         <v>-0</v>
@@ -7007,28 +7007,28 @@
         <v>0</v>
       </c>
       <c r="DC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD12" t="n">
         <v>0</v>
       </c>
       <c r="DE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF12" t="n">
-        <v>-0.05730873296736465</v>
+        <v>-0.01418052211676676</v>
       </c>
       <c r="DG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH12" t="n">
-        <v>0.0147528187533959</v>
+        <v>-0.007289570083439874</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.07094335858169661</v>
+        <v>-0.053459154489778</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK12" t="n">
         <v>-0</v>
@@ -7040,46 +7040,46 @@
         <v>0</v>
       </c>
       <c r="DN12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO12" t="n">
-        <v>-0.06141047062449132</v>
+        <v>-0.09431458747062245</v>
       </c>
       <c r="DP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ12" t="n">
-        <v>0.01337022886359442</v>
+        <v>0.07424181315678155</v>
       </c>
       <c r="DR12" t="n">
-        <v>-0.03829413678612164</v>
+        <v>0.01938867561277992</v>
       </c>
       <c r="DS12" t="n">
         <v>0</v>
       </c>
       <c r="DT12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX12" t="n">
-        <v>0.0431885914341151</v>
+        <v>0.04620730917392424</v>
       </c>
       <c r="DY12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ12" t="n">
-        <v>0.04070382045676444</v>
+        <v>-0.01644441472344636</v>
       </c>
       <c r="EA12" t="n">
-        <v>-0.01877070969609844</v>
+        <v>-0.05495732226998773</v>
       </c>
       <c r="EB12" t="n">
         <v>0</v>
@@ -7088,61 +7088,61 @@
         <v>-0</v>
       </c>
       <c r="ED12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE12" t="n">
         <v>-0</v>
       </c>
       <c r="EF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG12" t="n">
-        <v>-0.008189786439984623</v>
+        <v>-0.00302943473585272</v>
       </c>
       <c r="EH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI12" t="n">
-        <v>0.03507582479266349</v>
+        <v>0.06202920057571509</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.06104917869988355</v>
+        <v>0.0844015816964849</v>
       </c>
       <c r="EK12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN12" t="n">
         <v>-0</v>
       </c>
       <c r="EO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP12" t="n">
-        <v>-0.04529930119675849</v>
+        <v>-0.05553574658588602</v>
       </c>
       <c r="EQ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER12" t="n">
-        <v>0.0236647668648878</v>
+        <v>0.0650725204614213</v>
       </c>
       <c r="ES12" t="n">
-        <v>0.03866584567448064</v>
+        <v>-0.005956604911457722</v>
       </c>
       <c r="ET12" t="n">
         <v>-0</v>
       </c>
       <c r="EU12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW12" t="n">
         <v>-0</v>
@@ -7151,22 +7151,22 @@
         <v>-0</v>
       </c>
       <c r="EY12" t="n">
-        <v>-0.03796863712197205</v>
+        <v>-0.09203022918194635</v>
       </c>
       <c r="EZ12" t="n">
         <v>-0</v>
       </c>
       <c r="FA12" t="n">
-        <v>0.01072474915329128</v>
+        <v>0.0991316311711216</v>
       </c>
       <c r="FB12" t="n">
-        <v>0.007651782362332809</v>
+        <v>0.03724445049740187</v>
       </c>
       <c r="FC12" t="n">
         <v>-0</v>
       </c>
       <c r="FD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE12" t="n">
         <v>0</v>
@@ -7178,43 +7178,43 @@
         <v>-0</v>
       </c>
       <c r="FH12" t="n">
-        <v>0.05649532116580634</v>
+        <v>-0.02059223724947161</v>
       </c>
       <c r="FI12" t="n">
         <v>-0</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0.02074653506986128</v>
+        <v>0.005497677129220429</v>
       </c>
       <c r="FK12" t="n">
-        <v>-0.04069233845702301</v>
+        <v>-0.0453802803068168</v>
       </c>
       <c r="FL12" t="n">
         <v>-0</v>
       </c>
       <c r="FM12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ12" t="n">
-        <v>-0.05269487872635672</v>
+        <v>-0.0196285343946137</v>
       </c>
       <c r="FR12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS12" t="n">
-        <v>-0.05242776800701888</v>
+        <v>0.05211189378797636</v>
       </c>
       <c r="FT12" t="n">
-        <v>0.05945193313010842</v>
+        <v>-0.1152414097698474</v>
       </c>
       <c r="FU12" t="n">
         <v>-0</v>
@@ -7229,28 +7229,28 @@
         <v>0</v>
       </c>
       <c r="FY12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ12" t="n">
-        <v>-0.006112135077122285</v>
+        <v>-0.05914359370467627</v>
       </c>
       <c r="GA12" t="n">
         <v>-0</v>
       </c>
       <c r="GB12" t="n">
-        <v>-0.07491276865732255</v>
+        <v>0.03062053079629774</v>
       </c>
       <c r="GC12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG12" t="n">
         <v>-0</v>
@@ -7261,19 +7261,19 @@
         <v>0</v>
       </c>
       <c r="B13" t="n">
-        <v>0.4665621304668553</v>
+        <v>0.3839161416377304</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.1050421589734973</v>
+        <v>0.03944884571939139</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3798365090585497</v>
+        <v>-0.3439516607760076</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -7288,25 +7288,25 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0.3475950843924356</v>
+        <v>0.5466647597892828</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.08318547196511381</v>
+        <v>-0.009984647918669765</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.3576605702948973</v>
+        <v>-0.3277259501030891</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -7315,25 +7315,25 @@
         <v>-0</v>
       </c>
       <c r="T13" t="n">
-        <v>0.05146994832744293</v>
+        <v>0.1189328918650552</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.01510364759251233</v>
+        <v>-0.1971697222182063</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.01176666011136721</v>
+        <v>-0.05141620989546025</v>
       </c>
       <c r="Y13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -7342,19 +7342,19 @@
         <v>-0</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.06080335729691853</v>
+        <v>-0.02862934448077473</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.0391114020128145</v>
+        <v>-0.3751063663443819</v>
       </c>
       <c r="AG13" t="n">
-        <v>-0.04017455391896687</v>
+        <v>-0.2425534042032605</v>
       </c>
       <c r="AH13" t="n">
         <v>-0</v>
@@ -7369,7 +7369,7 @@
         <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.06362746318441122</v>
+        <v>0.0825638821098109</v>
       </c>
       <c r="AM13" t="n">
         <v>0</v>
@@ -7378,13 +7378,13 @@
         <v>0</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.001006772383745671</v>
+        <v>-0.04195826674539314</v>
       </c>
       <c r="AP13" t="n">
-        <v>-0.06720074416303581</v>
+        <v>-0.1539809442557787</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR13" t="n">
         <v>-0</v>
@@ -7393,10 +7393,10 @@
         <v>0</v>
       </c>
       <c r="AT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.375167771239022</v>
+        <v>0.8134498294636215</v>
       </c>
       <c r="AV13" t="n">
         <v>-0</v>
@@ -7405,16 +7405,16 @@
         <v>0</v>
       </c>
       <c r="AX13" t="n">
-        <v>-0.02053269586224446</v>
+        <v>-0.1507476273353652</v>
       </c>
       <c r="AY13" t="n">
-        <v>-0.1674139266135458</v>
+        <v>-0.1529440810675047</v>
       </c>
       <c r="AZ13" t="n">
         <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB13" t="n">
         <v>0</v>
@@ -7423,49 +7423,49 @@
         <v>0</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.1253273287919058</v>
+        <v>-0.147285327163815</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF13" t="n">
         <v>0</v>
       </c>
       <c r="BG13" t="n">
-        <v>-0.104227551371531</v>
+        <v>-0.1323971939178514</v>
       </c>
       <c r="BH13" t="n">
-        <v>-0.1276149032896083</v>
+        <v>-0.1946057062657676</v>
       </c>
       <c r="BI13" t="n">
         <v>0</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.1360660032589155</v>
+        <v>0.1159394185487524</v>
       </c>
       <c r="BN13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO13" t="n">
         <v>-0</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.07527654616142156</v>
+        <v>0.113686179624782</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0.02855342291944482</v>
+        <v>0.002316958225156421</v>
       </c>
       <c r="BR13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS13" t="n">
         <v>0</v>
@@ -7474,76 +7474,76 @@
         <v>-0</v>
       </c>
       <c r="BU13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.2020884531697853</v>
+        <v>0.4117106320728016</v>
       </c>
       <c r="BW13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX13" t="n">
         <v>0</v>
       </c>
       <c r="BY13" t="n">
-        <v>-0.04455259827693758</v>
+        <v>-0.2194503037256448</v>
       </c>
       <c r="BZ13" t="n">
-        <v>-0.1118710102516323</v>
+        <v>-0.2672665820565694</v>
       </c>
       <c r="CA13" t="n">
         <v>-0</v>
       </c>
       <c r="CB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC13" t="n">
         <v>0</v>
       </c>
       <c r="CD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE13" t="n">
-        <v>-0.08825863448527281</v>
+        <v>-0.147415421163609</v>
       </c>
       <c r="CF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH13" t="n">
-        <v>-0.006407981680952734</v>
+        <v>0.05919673826153991</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.08321333525911236</v>
+        <v>0.1419941951340163</v>
       </c>
       <c r="CJ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK13" t="n">
         <v>0</v>
       </c>
       <c r="CL13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM13" t="n">
         <v>0</v>
       </c>
       <c r="CN13" t="n">
-        <v>-0.08734395907042281</v>
+        <v>-0.3897703606402514</v>
       </c>
       <c r="CO13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ13" t="n">
-        <v>-0.03140158486791071</v>
+        <v>0.4375724395659444</v>
       </c>
       <c r="CR13" t="n">
-        <v>-0.009433444400432887</v>
+        <v>0.3196358394955505</v>
       </c>
       <c r="CS13" t="n">
         <v>-0</v>
@@ -7558,103 +7558,103 @@
         <v>-0</v>
       </c>
       <c r="CW13" t="n">
-        <v>-0.0657357479466322</v>
+        <v>-0.1372487318627551</v>
       </c>
       <c r="CX13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY13" t="n">
         <v>0</v>
       </c>
       <c r="CZ13" t="n">
-        <v>-0.005282047057217411</v>
+        <v>0.02407496568761807</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.08589172134791066</v>
+        <v>0.1101038004861669</v>
       </c>
       <c r="DB13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC13" t="n">
         <v>-0</v>
       </c>
       <c r="DD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF13" t="n">
-        <v>-0.06771428612008003</v>
+        <v>-0.001330649390839775</v>
       </c>
       <c r="DG13" t="n">
         <v>0</v>
       </c>
       <c r="DH13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.02396704723663188</v>
+        <v>-0.1139694507164453</v>
       </c>
       <c r="DJ13" t="n">
-        <v>0.0222797968767464</v>
+        <v>-0.008155784338289068</v>
       </c>
       <c r="DK13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM13" t="n">
         <v>0</v>
       </c>
       <c r="DN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO13" t="n">
-        <v>-0.0542955967436283</v>
+        <v>0.006087090526769451</v>
       </c>
       <c r="DP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.03061163933193488</v>
+        <v>0.02721409102460203</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.01058518790685225</v>
+        <v>0.08278028105968768</v>
       </c>
       <c r="DT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW13" t="n">
         <v>-0</v>
       </c>
       <c r="DX13" t="n">
-        <v>0.008614851019512929</v>
+        <v>0.1214387964881171</v>
       </c>
       <c r="DY13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ13" t="n">
         <v>-0</v>
       </c>
       <c r="EA13" t="n">
-        <v>0.006730768323058503</v>
+        <v>-0.03067049966428613</v>
       </c>
       <c r="EB13" t="n">
-        <v>0.03318324491840238</v>
+        <v>0.07116378943156662</v>
       </c>
       <c r="EC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED13" t="n">
         <v>-0</v>
@@ -7666,34 +7666,34 @@
         <v>0</v>
       </c>
       <c r="EG13" t="n">
-        <v>-0.03524041805942586</v>
+        <v>-0.04766565405578165</v>
       </c>
       <c r="EH13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.01741738607522207</v>
+        <v>-0.04415822341194802</v>
       </c>
       <c r="EK13" t="n">
-        <v>0.07012310578256475</v>
+        <v>0.007191573569859664</v>
       </c>
       <c r="EL13" t="n">
         <v>-0</v>
       </c>
       <c r="EM13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP13" t="n">
-        <v>-0.01660764276269707</v>
+        <v>0.007372069540026361</v>
       </c>
       <c r="EQ13" t="n">
         <v>0</v>
@@ -7702,13 +7702,13 @@
         <v>-0</v>
       </c>
       <c r="ES13" t="n">
-        <v>-0.007533997115604164</v>
+        <v>-0.01908979061918969</v>
       </c>
       <c r="ET13" t="n">
-        <v>0.07471318898621125</v>
+        <v>0.1300396468433327</v>
       </c>
       <c r="EU13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV13" t="n">
         <v>0</v>
@@ -7717,55 +7717,55 @@
         <v>-0</v>
       </c>
       <c r="EX13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY13" t="n">
-        <v>-0.0601727225160874</v>
+        <v>-0.1706856221129418</v>
       </c>
       <c r="EZ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA13" t="n">
         <v>-0</v>
       </c>
       <c r="FB13" t="n">
-        <v>-0.001130900462296355</v>
+        <v>0.0146702472931285</v>
       </c>
       <c r="FC13" t="n">
-        <v>0.08591831130363328</v>
+        <v>0.1243335112455781</v>
       </c>
       <c r="FD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE13" t="n">
         <v>0</v>
       </c>
       <c r="FF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG13" t="n">
         <v>0</v>
       </c>
       <c r="FH13" t="n">
-        <v>-0.04960370416953896</v>
+        <v>-0.1799544245702237</v>
       </c>
       <c r="FI13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ13" t="n">
         <v>-0</v>
       </c>
       <c r="FK13" t="n">
-        <v>-0.01424661583233029</v>
+        <v>0.07592468060048474</v>
       </c>
       <c r="FL13" t="n">
-        <v>-0.04825260597194534</v>
+        <v>-0.04865768935724935</v>
       </c>
       <c r="FM13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO13" t="n">
         <v>0</v>
@@ -7774,46 +7774,46 @@
         <v>0</v>
       </c>
       <c r="FQ13" t="n">
-        <v>0.01040502680258809</v>
+        <v>0.05979434335537398</v>
       </c>
       <c r="FR13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS13" t="n">
         <v>-0</v>
       </c>
       <c r="FT13" t="n">
-        <v>-0.04416228011876092</v>
+        <v>0.07065702589999953</v>
       </c>
       <c r="FU13" t="n">
-        <v>-0.01197027907342603</v>
+        <v>-0.02723237010840799</v>
       </c>
       <c r="FV13" t="n">
         <v>-0</v>
       </c>
       <c r="FW13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ13" t="n">
-        <v>-0.02666276518072906</v>
+        <v>-0.04307282649126368</v>
       </c>
       <c r="GA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB13" t="n">
         <v>-0</v>
       </c>
       <c r="GC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD13" t="n">
-        <v>-0.03656540227212324</v>
+        <v>0.06850752289549872</v>
       </c>
       <c r="GE13" t="n">
         <v>-0</v>
@@ -7822,7 +7822,7 @@
         <v>-0</v>
       </c>
       <c r="GG13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -7830,16 +7830,16 @@
         <v>0</v>
       </c>
       <c r="B14" t="n">
-        <v>0.5510545727633092</v>
+        <v>0.2912344235296073</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.1758324647836556</v>
+        <v>-0.1909252223810358</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.1579047206825233</v>
+        <v>-0.07223758414336687</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -7851,22 +7851,22 @@
         <v>-0</v>
       </c>
       <c r="I14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K14" t="n">
-        <v>0.3380761022927478</v>
+        <v>0.2818660578846993</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.1377646098911542</v>
+        <v>-0.2218730815904041</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.1394680784956407</v>
+        <v>-0.1695002363486062</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -7881,73 +7881,73 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1045988644638824</v>
+        <v>0.04916755615041413</v>
       </c>
       <c r="U14" t="n">
         <v>-0</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.0210509296809802</v>
+        <v>-0.03908070989414824</v>
       </c>
       <c r="W14" t="n">
-        <v>0.04225315524227074</v>
+        <v>-0.07828129248834793</v>
       </c>
       <c r="X14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
         <v>-0</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.105485255683727</v>
+        <v>0.023665645131596</v>
       </c>
       <c r="AD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.003083320401866868</v>
+        <v>-0.1981171635193382</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.003697119932299389</v>
+        <v>-0.1411274877417415</v>
       </c>
       <c r="AG14" t="n">
         <v>-0</v>
       </c>
       <c r="AH14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.0126788771290071</v>
+        <v>0.164447358146764</v>
       </c>
       <c r="AM14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>-0.07237398149077609</v>
+        <v>-0.1078284103108293</v>
       </c>
       <c r="AO14" t="n">
-        <v>-0.09153939822678707</v>
+        <v>0.0639187129261381</v>
       </c>
       <c r="AP14" t="n">
         <v>0</v>
@@ -7962,79 +7962,79 @@
         <v>0</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.4373458854493958</v>
+        <v>0.3671259096917128</v>
       </c>
       <c r="AV14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.04968077896957774</v>
+        <v>-0.02941606697621782</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.05955317479811895</v>
+        <v>-0.3192498126129911</v>
       </c>
       <c r="AY14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB14" t="n">
         <v>-0</v>
       </c>
       <c r="BC14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD14" t="n">
-        <v>0.02663723620754396</v>
+        <v>-0.02060399392929339</v>
       </c>
       <c r="BE14" t="n">
         <v>0</v>
       </c>
       <c r="BF14" t="n">
-        <v>-0.09165541383501924</v>
+        <v>-0.06339234959513952</v>
       </c>
       <c r="BG14" t="n">
-        <v>-0.2087453833995604</v>
+        <v>0.07042789396804301</v>
       </c>
       <c r="BH14" t="n">
         <v>0</v>
       </c>
       <c r="BI14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL14" t="n">
         <v>-0</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.1194612235442133</v>
+        <v>0.08846200812662386</v>
       </c>
       <c r="BN14" t="n">
         <v>-0</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.04786076591424689</v>
+        <v>0.02363844567463865</v>
       </c>
       <c r="BP14" t="n">
-        <v>0.1429394721231063</v>
+        <v>0.13483657472773</v>
       </c>
       <c r="BQ14" t="n">
         <v>-0</v>
       </c>
       <c r="BR14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS14" t="n">
         <v>-0</v>
@@ -8043,46 +8043,46 @@
         <v>-0</v>
       </c>
       <c r="BU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV14" t="n">
-        <v>0.2116740377713686</v>
+        <v>0.2925517434208127</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>0.0567644346339902</v>
+        <v>-0.1287165727127638</v>
       </c>
       <c r="BY14" t="n">
-        <v>0.02093818732326761</v>
+        <v>-0.1160258590622096</v>
       </c>
       <c r="BZ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA14" t="n">
         <v>-0</v>
       </c>
       <c r="CB14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE14" t="n">
-        <v>-0.1160284367411193</v>
+        <v>-0.09626680350019276</v>
       </c>
       <c r="CF14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG14" t="n">
-        <v>0.01388354741492934</v>
+        <v>0.1017426844867311</v>
       </c>
       <c r="CH14" t="n">
-        <v>-0.01539804547200292</v>
+        <v>0.07026531120884759</v>
       </c>
       <c r="CI14" t="n">
         <v>-0</v>
@@ -8100,16 +8100,16 @@
         <v>0</v>
       </c>
       <c r="CN14" t="n">
-        <v>-0.01056033382867436</v>
+        <v>-0.2214871092811696</v>
       </c>
       <c r="CO14" t="n">
         <v>-0</v>
       </c>
       <c r="CP14" t="n">
-        <v>-0.1049667669879633</v>
+        <v>0.2693058810871261</v>
       </c>
       <c r="CQ14" t="n">
-        <v>-0.09001555348937813</v>
+        <v>0.147444558393542</v>
       </c>
       <c r="CR14" t="n">
         <v>0</v>
@@ -8121,22 +8121,22 @@
         <v>-0</v>
       </c>
       <c r="CU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV14" t="n">
         <v>0</v>
       </c>
       <c r="CW14" t="n">
-        <v>-0.09341672102454733</v>
+        <v>-0.07485510441815481</v>
       </c>
       <c r="CX14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY14" t="n">
-        <v>0.0351969519486122</v>
+        <v>0.1225611722775161</v>
       </c>
       <c r="CZ14" t="n">
-        <v>-0.01784944714434282</v>
+        <v>0.08058544072270821</v>
       </c>
       <c r="DA14" t="n">
         <v>0</v>
@@ -8154,22 +8154,22 @@
         <v>0</v>
       </c>
       <c r="DF14" t="n">
-        <v>0.004123261275330501</v>
+        <v>0.0003265135178373345</v>
       </c>
       <c r="DG14" t="n">
         <v>0</v>
       </c>
       <c r="DH14" t="n">
-        <v>0.02219735002350104</v>
+        <v>0.01034690693887763</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.03458721926693872</v>
+        <v>-0.05442717289460591</v>
       </c>
       <c r="DJ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL14" t="n">
         <v>0</v>
@@ -8178,46 +8178,46 @@
         <v>0</v>
       </c>
       <c r="DN14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO14" t="n">
-        <v>-0.04388295922739893</v>
+        <v>-0.1453151588715363</v>
       </c>
       <c r="DP14" t="n">
         <v>0</v>
       </c>
       <c r="DQ14" t="n">
-        <v>0.06527442517556514</v>
+        <v>-0.07548864788413553</v>
       </c>
       <c r="DR14" t="n">
-        <v>-0.0622802181275218</v>
+        <v>0.02370437992708521</v>
       </c>
       <c r="DS14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT14" t="n">
         <v>-0</v>
       </c>
       <c r="DU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX14" t="n">
-        <v>0.03510095016547504</v>
+        <v>0.05619726595456628</v>
       </c>
       <c r="DY14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ14" t="n">
-        <v>-0.001838232754058247</v>
+        <v>0.01260390279228724</v>
       </c>
       <c r="EA14" t="n">
-        <v>-0.08335579725466342</v>
+        <v>-0.1683776348281699</v>
       </c>
       <c r="EB14" t="n">
         <v>0</v>
@@ -8229,31 +8229,31 @@
         <v>0</v>
       </c>
       <c r="EE14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG14" t="n">
-        <v>-0.09873466561788502</v>
+        <v>0.02326676058116166</v>
       </c>
       <c r="EH14" t="n">
         <v>0</v>
       </c>
       <c r="EI14" t="n">
-        <v>0.03752483748216181</v>
+        <v>0.05804587377529758</v>
       </c>
       <c r="EJ14" t="n">
-        <v>0.08233427732548619</v>
+        <v>0.09483203428550101</v>
       </c>
       <c r="EK14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL14" t="n">
         <v>-0</v>
       </c>
       <c r="EM14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN14" t="n">
         <v>-0</v>
@@ -8262,22 +8262,22 @@
         <v>0</v>
       </c>
       <c r="EP14" t="n">
-        <v>-0.06681668771123532</v>
+        <v>-0.05068618637321072</v>
       </c>
       <c r="EQ14" t="n">
         <v>0</v>
       </c>
       <c r="ER14" t="n">
-        <v>0.02719126345673609</v>
+        <v>0.08551563764451259</v>
       </c>
       <c r="ES14" t="n">
-        <v>0.01793925719140006</v>
+        <v>-0.06895653887275517</v>
       </c>
       <c r="ET14" t="n">
         <v>-0</v>
       </c>
       <c r="EU14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV14" t="n">
         <v>0</v>
@@ -8286,73 +8286,73 @@
         <v>-0</v>
       </c>
       <c r="EX14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY14" t="n">
-        <v>-0.09495810294369821</v>
+        <v>-0.09877035005670191</v>
       </c>
       <c r="EZ14" t="n">
         <v>-0</v>
       </c>
       <c r="FA14" t="n">
-        <v>0.02431244505785948</v>
+        <v>0.1258851783303071</v>
       </c>
       <c r="FB14" t="n">
-        <v>0.01020310731179171</v>
+        <v>0.06219693990238202</v>
       </c>
       <c r="FC14" t="n">
         <v>-0</v>
       </c>
       <c r="FD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE14" t="n">
         <v>0</v>
       </c>
       <c r="FF14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH14" t="n">
-        <v>-0.001585774585808661</v>
+        <v>0.004460815833238306</v>
       </c>
       <c r="FI14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ14" t="n">
-        <v>0.07431937727075238</v>
+        <v>0.05069229188557855</v>
       </c>
       <c r="FK14" t="n">
-        <v>-0.08642680355221523</v>
+        <v>-0.01146269785270009</v>
       </c>
       <c r="FL14" t="n">
         <v>-0</v>
       </c>
       <c r="FM14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO14" t="n">
         <v>0</v>
       </c>
       <c r="FP14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ14" t="n">
-        <v>-0.008371896577597855</v>
+        <v>-0.004358124838650584</v>
       </c>
       <c r="FR14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS14" t="n">
-        <v>-0.01722261811518054</v>
+        <v>0.06951221633853241</v>
       </c>
       <c r="FT14" t="n">
-        <v>-0.01498037652753454</v>
+        <v>-0.05400230075867885</v>
       </c>
       <c r="FU14" t="n">
         <v>-0</v>
@@ -8361,34 +8361,34 @@
         <v>0</v>
       </c>
       <c r="FW14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX14" t="n">
         <v>0</v>
       </c>
       <c r="FY14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ14" t="n">
-        <v>0.005680393313427879</v>
+        <v>-0.07090341753419391</v>
       </c>
       <c r="GA14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB14" t="n">
-        <v>-0.06444579431684745</v>
+        <v>0.05936701952070136</v>
       </c>
       <c r="GC14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG14" t="n">
         <v>-0</v>
@@ -8396,22 +8396,22 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B15" t="n">
-        <v>0.5042019061187226</v>
+        <v>0.2333841905376789</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1648163550993095</v>
+        <v>-0.1869414824142452</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.2302475940318286</v>
+        <v>0.07105017280041691</v>
       </c>
       <c r="F15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
         <v>-0</v>
@@ -8426,16 +8426,16 @@
         <v>-0</v>
       </c>
       <c r="K15" t="n">
-        <v>0.4165475737397498</v>
+        <v>0.237162286626505</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.1533362540572669</v>
+        <v>-0.1865539114351334</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.2155408273981144</v>
+        <v>0.03052775951484475</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -8444,7 +8444,7 @@
         <v>-0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -8453,19 +8453,19 @@
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1051202290685186</v>
+        <v>0.09596408807509758</v>
       </c>
       <c r="U15" t="n">
         <v>-0</v>
       </c>
       <c r="V15" t="n">
-        <v>0.02189053973875994</v>
+        <v>-0.05201671137042382</v>
       </c>
       <c r="W15" t="n">
-        <v>0.0415812082830426</v>
+        <v>-0.03512305924471228</v>
       </c>
       <c r="X15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
         <v>-0</v>
@@ -8477,79 +8477,79 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.1600146544437294</v>
+        <v>-0.07821671864054783</v>
       </c>
       <c r="AD15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>-0.03377682627995913</v>
+        <v>-0.09069017533496461</v>
       </c>
       <c r="AF15" t="n">
-        <v>-0.001847176035024953</v>
+        <v>-7.057263546416504e-05</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
         <v>-0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
         <v>0</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.04454801081111021</v>
+        <v>0.06044623767991006</v>
       </c>
       <c r="AM15" t="n">
         <v>-0</v>
       </c>
       <c r="AN15" t="n">
-        <v>-0.01028759251675942</v>
+        <v>-0.09469860110496515</v>
       </c>
       <c r="AO15" t="n">
-        <v>-0.06203623988097771</v>
+        <v>0.06554304083295037</v>
       </c>
       <c r="AP15" t="n">
         <v>0</v>
       </c>
       <c r="AQ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR15" t="n">
         <v>-0</v>
       </c>
       <c r="AS15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT15" t="n">
         <v>-0</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.4139190905738754</v>
+        <v>0.2898768075358096</v>
       </c>
       <c r="AV15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.03612820895401574</v>
+        <v>-0.1820667094538918</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.04452731182416555</v>
+        <v>-0.0648976669944769</v>
       </c>
       <c r="AY15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA15" t="n">
         <v>0</v>
@@ -8558,25 +8558,25 @@
         <v>-0</v>
       </c>
       <c r="BC15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD15" t="n">
-        <v>0.03979667438347437</v>
+        <v>-0.05617955304525202</v>
       </c>
       <c r="BE15" t="n">
         <v>0</v>
       </c>
       <c r="BF15" t="n">
-        <v>-0.0824288984936787</v>
+        <v>-0.05410644775568325</v>
       </c>
       <c r="BG15" t="n">
-        <v>-0.2030130615397683</v>
+        <v>-0.01656573576886289</v>
       </c>
       <c r="BH15" t="n">
         <v>0</v>
       </c>
       <c r="BI15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ15" t="n">
         <v>-0</v>
@@ -8588,25 +8588,25 @@
         <v>-0</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.08036800609527707</v>
+        <v>0.01149922254981602</v>
       </c>
       <c r="BN15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO15" t="n">
-        <v>0.01942899971220466</v>
+        <v>0.008200732301791089</v>
       </c>
       <c r="BP15" t="n">
-        <v>0.07902544403026353</v>
+        <v>0.03804903548361115</v>
       </c>
       <c r="BQ15" t="n">
         <v>-0</v>
       </c>
       <c r="BR15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT15" t="n">
         <v>-0</v>
@@ -8615,22 +8615,22 @@
         <v>-0</v>
       </c>
       <c r="BV15" t="n">
-        <v>0.2564920173166301</v>
+        <v>0.1844480470476515</v>
       </c>
       <c r="BW15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX15" t="n">
-        <v>-0.005867021994631369</v>
+        <v>-0.1130544995288139</v>
       </c>
       <c r="BY15" t="n">
-        <v>0.0424117734659945</v>
+        <v>-0.01272432235129844</v>
       </c>
       <c r="BZ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB15" t="n">
         <v>0</v>
@@ -8642,19 +8642,19 @@
         <v>0</v>
       </c>
       <c r="CE15" t="n">
-        <v>-0.09276998947227159</v>
+        <v>-0.05245179299469936</v>
       </c>
       <c r="CF15" t="n">
         <v>-0</v>
       </c>
       <c r="CG15" t="n">
-        <v>0.02281940164936659</v>
+        <v>0.07601937212568756</v>
       </c>
       <c r="CH15" t="n">
-        <v>0.01408208424647766</v>
+        <v>0.002301593462521457</v>
       </c>
       <c r="CI15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ15" t="n">
         <v>-0</v>
@@ -8669,19 +8669,19 @@
         <v>0</v>
       </c>
       <c r="CN15" t="n">
-        <v>-0.07712309901056921</v>
+        <v>-0.085288429612759</v>
       </c>
       <c r="CO15" t="n">
         <v>-0</v>
       </c>
       <c r="CP15" t="n">
-        <v>-0.05034424638398825</v>
+        <v>0.1925983800994762</v>
       </c>
       <c r="CQ15" t="n">
-        <v>-0.1381307957155735</v>
+        <v>0.1367715309917922</v>
       </c>
       <c r="CR15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS15" t="n">
         <v>-0</v>
@@ -8693,19 +8693,19 @@
         <v>-0</v>
       </c>
       <c r="CV15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW15" t="n">
-        <v>-0.06931748166088583</v>
+        <v>-0.05151614824255113</v>
       </c>
       <c r="CX15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY15" t="n">
-        <v>0.03232229259586932</v>
+        <v>0.0918808490893926</v>
       </c>
       <c r="CZ15" t="n">
-        <v>0.01102203140620761</v>
+        <v>0.002500645245955579</v>
       </c>
       <c r="DA15" t="n">
         <v>0</v>
@@ -8714,7 +8714,7 @@
         <v>0</v>
       </c>
       <c r="DC15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD15" t="n">
         <v>0</v>
@@ -8723,16 +8723,16 @@
         <v>0</v>
       </c>
       <c r="DF15" t="n">
-        <v>-0.01943646959995355</v>
+        <v>-0.02728462176485044</v>
       </c>
       <c r="DG15" t="n">
         <v>-0</v>
       </c>
       <c r="DH15" t="n">
-        <v>0.02208548686082589</v>
+        <v>-0.00271028193697959</v>
       </c>
       <c r="DI15" t="n">
-        <v>-0.002331226893112591</v>
+        <v>0.000307711534969135</v>
       </c>
       <c r="DJ15" t="n">
         <v>0</v>
@@ -8744,22 +8744,22 @@
         <v>0</v>
       </c>
       <c r="DM15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO15" t="n">
-        <v>-0.02462360016664726</v>
+        <v>-0.02835986887358168</v>
       </c>
       <c r="DP15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ15" t="n">
-        <v>-0.03308998652850587</v>
+        <v>0.007959044146816207</v>
       </c>
       <c r="DR15" t="n">
-        <v>-0.0280888729911582</v>
+        <v>0.009316974295975174</v>
       </c>
       <c r="DS15" t="n">
         <v>-0</v>
@@ -8768,34 +8768,34 @@
         <v>-0</v>
       </c>
       <c r="DU15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV15" t="n">
         <v>0</v>
       </c>
       <c r="DW15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX15" t="n">
-        <v>0.04972552876885833</v>
+        <v>0.02560574251062196</v>
       </c>
       <c r="DY15" t="n">
         <v>-0</v>
       </c>
       <c r="DZ15" t="n">
-        <v>-0.0362535444211706</v>
+        <v>-0.02136475771440281</v>
       </c>
       <c r="EA15" t="n">
-        <v>0.002214879617914185</v>
+        <v>0.005906405597000839</v>
       </c>
       <c r="EB15" t="n">
         <v>0</v>
       </c>
       <c r="EC15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE15" t="n">
         <v>-0</v>
@@ -8804,25 +8804,25 @@
         <v>0</v>
       </c>
       <c r="EG15" t="n">
-        <v>-0.07501441528007886</v>
+        <v>-0.06835622298864652</v>
       </c>
       <c r="EH15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI15" t="n">
-        <v>0.05133164896802291</v>
+        <v>0.06241240281408901</v>
       </c>
       <c r="EJ15" t="n">
-        <v>0.07547912683882237</v>
+        <v>0.03138395352211463</v>
       </c>
       <c r="EK15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL15" t="n">
         <v>-0</v>
       </c>
       <c r="EM15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN15" t="n">
         <v>-0</v>
@@ -8831,16 +8831,16 @@
         <v>0</v>
       </c>
       <c r="EP15" t="n">
-        <v>-0.05431554385521863</v>
+        <v>-0.01606036268894086</v>
       </c>
       <c r="EQ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER15" t="n">
-        <v>0.0236157549512712</v>
+        <v>0.03974543001276048</v>
       </c>
       <c r="ES15" t="n">
-        <v>0.07974915538730297</v>
+        <v>0.01049134434283228</v>
       </c>
       <c r="ET15" t="n">
         <v>-0</v>
@@ -8858,22 +8858,22 @@
         <v>0</v>
       </c>
       <c r="EY15" t="n">
-        <v>-0.07684382784263072</v>
+        <v>-0.07405287152093819</v>
       </c>
       <c r="EZ15" t="n">
         <v>-0</v>
       </c>
       <c r="FA15" t="n">
-        <v>0.04197804094994189</v>
+        <v>0.09104555811568353</v>
       </c>
       <c r="FB15" t="n">
-        <v>0.01521829424323854</v>
+        <v>0.0007630806886260192</v>
       </c>
       <c r="FC15" t="n">
         <v>-0</v>
       </c>
       <c r="FD15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE15" t="n">
         <v>0</v>
@@ -8882,46 +8882,46 @@
         <v>-0</v>
       </c>
       <c r="FG15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH15" t="n">
-        <v>-0.004518288790913454</v>
+        <v>-0.0352960491030968</v>
       </c>
       <c r="FI15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ15" t="n">
-        <v>0.06073639346552966</v>
+        <v>0.09463107667931181</v>
       </c>
       <c r="FK15" t="n">
-        <v>-0.05502135839099695</v>
+        <v>-0.02968845051710823</v>
       </c>
       <c r="FL15" t="n">
         <v>-0</v>
       </c>
       <c r="FM15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN15" t="n">
         <v>0</v>
       </c>
       <c r="FO15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FP15" t="n">
         <v>-0</v>
       </c>
       <c r="FQ15" t="n">
-        <v>-0.009263285713766802</v>
+        <v>-0.01398370472609964</v>
       </c>
       <c r="FR15" t="n">
         <v>-0</v>
       </c>
       <c r="FS15" t="n">
-        <v>-0.1297497523112299</v>
+        <v>-0.1536199504135683</v>
       </c>
       <c r="FT15" t="n">
-        <v>0.0176017700755606</v>
+        <v>-0.01617448742156081</v>
       </c>
       <c r="FU15" t="n">
         <v>-0</v>
@@ -8933,31 +8933,31 @@
         <v>0</v>
       </c>
       <c r="FX15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ15" t="n">
-        <v>-0.02970438109530304</v>
+        <v>-0.07327426860791089</v>
       </c>
       <c r="GA15" t="n">
         <v>0</v>
       </c>
       <c r="GB15" t="n">
-        <v>-0.03634370604425367</v>
+        <v>0.06781132698065523</v>
       </c>
       <c r="GC15" t="n">
         <v>-0</v>
       </c>
       <c r="GD15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE15" t="n">
         <v>-0</v>
       </c>
       <c r="GF15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG15" t="n">
         <v>-0</v>
